--- a/research/traditional_assets/database/data/pakistan/pakistan_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_beverage_alcoholic.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1587997630207022</v>
+        <v>0.1583711937079421</v>
       </c>
       <c r="C2">
-        <v>71.54477982325332</v>
+        <v>71.02057112642686</v>
       </c>
       <c r="D2">
-        <v>58.04477982325332</v>
+        <v>58.23583112642686</v>
       </c>
       <c r="E2">
-        <v>-0.126</v>
+        <v>0.5892600000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.7152600000000001</v>
       </c>
       <c r="G2">
         <v>13.5</v>
@@ -1451,28 +1451,28 @@
         <v>13.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.035977578</v>
       </c>
       <c r="N2">
-        <v>13.5</v>
+        <v>13.464022422</v>
       </c>
       <c r="O2">
-        <v>3.915</v>
+        <v>3.904566502379999</v>
       </c>
       <c r="P2">
-        <v>9.585000000000001</v>
+        <v>9.55945591962</v>
       </c>
       <c r="Q2">
-        <v>11.085</v>
+        <v>11.05945591962</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1587997630207022</v>
+        <v>0.1596101653615577</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905985</v>
+        <v>0.6960488037245613</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>375.2337080611707</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1583711937079421</v>
+        <v>0.1579426243951821</v>
       </c>
       <c r="C3">
-        <v>71.02057112642686</v>
+        <v>70.49762425321588</v>
       </c>
       <c r="D3">
-        <v>58.23583112642686</v>
+        <v>58.42814425321588</v>
       </c>
       <c r="E3">
-        <v>0.5892600000000001</v>
+        <v>1.30452</v>
       </c>
       <c r="F3">
-        <v>0.7152600000000001</v>
+        <v>1.43052</v>
       </c>
       <c r="G3">
         <v>13.5</v>
@@ -1533,28 +1533,28 @@
         <v>13.5</v>
       </c>
       <c r="M3">
-        <v>0.035977578</v>
+        <v>0.07195515600000001</v>
       </c>
       <c r="N3">
-        <v>13.464022422</v>
+        <v>13.428044844</v>
       </c>
       <c r="O3">
-        <v>3.904566502379999</v>
+        <v>3.89413300476</v>
       </c>
       <c r="P3">
-        <v>9.55945591962</v>
+        <v>9.53391183924</v>
       </c>
       <c r="Q3">
-        <v>11.05945591962</v>
+        <v>11.03391183924</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1596101653615577</v>
+        <v>0.160437106525696</v>
       </c>
       <c r="T3">
-        <v>0.6960488037245613</v>
+        <v>0.701106272942891</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>375.2337080611707</v>
+        <v>187.6168540305854</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1579426243951821</v>
+        <v>0.1575140550824221</v>
       </c>
       <c r="C4">
-        <v>70.49762425321588</v>
+        <v>69.97595174586036</v>
       </c>
       <c r="D4">
-        <v>58.42814425321588</v>
+        <v>58.62173174586035</v>
       </c>
       <c r="E4">
-        <v>1.30452</v>
+        <v>2.01978</v>
       </c>
       <c r="F4">
-        <v>1.43052</v>
+        <v>2.14578</v>
       </c>
       <c r="G4">
         <v>13.5</v>
@@ -1615,28 +1615,28 @@
         <v>13.5</v>
       </c>
       <c r="M4">
-        <v>0.07195515600000001</v>
+        <v>0.107932734</v>
       </c>
       <c r="N4">
-        <v>13.428044844</v>
+        <v>13.392067266</v>
       </c>
       <c r="O4">
-        <v>3.89413300476</v>
+        <v>3.88369950714</v>
       </c>
       <c r="P4">
-        <v>9.53391183924</v>
+        <v>9.50836775886</v>
       </c>
       <c r="Q4">
-        <v>11.03391183924</v>
+        <v>11.00836775886</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.160437106525696</v>
+        <v>0.1612810980231155</v>
       </c>
       <c r="T4">
-        <v>0.701106272942891</v>
+        <v>0.7062680198770622</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>187.6168540305854</v>
+        <v>125.0779026870569</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1575140550824221</v>
+        <v>0.157085485769662</v>
       </c>
       <c r="C5">
-        <v>69.97595174586036</v>
+        <v>69.45556631337561</v>
       </c>
       <c r="D5">
-        <v>58.62173174586035</v>
+        <v>58.81660631337561</v>
       </c>
       <c r="E5">
-        <v>2.01978</v>
+        <v>2.735040000000001</v>
       </c>
       <c r="F5">
-        <v>2.14578</v>
+        <v>2.86104</v>
       </c>
       <c r="G5">
         <v>13.5</v>
@@ -1697,28 +1697,28 @@
         <v>13.5</v>
       </c>
       <c r="M5">
-        <v>0.107932734</v>
+        <v>0.143910312</v>
       </c>
       <c r="N5">
-        <v>13.392067266</v>
+        <v>13.356089688</v>
       </c>
       <c r="O5">
-        <v>3.88369950714</v>
+        <v>3.87326600952</v>
       </c>
       <c r="P5">
-        <v>9.50836775886</v>
+        <v>9.482823678480001</v>
       </c>
       <c r="Q5">
-        <v>11.00836775886</v>
+        <v>10.98282367848</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1612810980231155</v>
+        <v>0.1621426726767313</v>
       </c>
       <c r="T5">
-        <v>0.7062680198770622</v>
+        <v>0.7115373032056954</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>125.0779026870569</v>
+        <v>93.80842701529269</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.157085485769662</v>
+        <v>0.156656916456902</v>
       </c>
       <c r="C6">
-        <v>69.45556631337561</v>
+        <v>68.93648083433344</v>
       </c>
       <c r="D6">
-        <v>58.81660631337561</v>
+        <v>59.01278083433344</v>
       </c>
       <c r="E6">
-        <v>2.735040000000001</v>
+        <v>3.450300000000001</v>
       </c>
       <c r="F6">
-        <v>2.86104</v>
+        <v>3.576300000000001</v>
       </c>
       <c r="G6">
         <v>13.5</v>
@@ -1779,28 +1779,28 @@
         <v>13.5</v>
       </c>
       <c r="M6">
-        <v>0.143910312</v>
+        <v>0.17988789</v>
       </c>
       <c r="N6">
-        <v>13.356089688</v>
+        <v>13.32011211</v>
       </c>
       <c r="O6">
-        <v>3.87326600952</v>
+        <v>3.8628325119</v>
       </c>
       <c r="P6">
-        <v>9.482823678480001</v>
+        <v>9.457279598100001</v>
       </c>
       <c r="Q6">
-        <v>10.98282367848</v>
+        <v>10.9572795981</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1621426726767313</v>
+        <v>0.1630223857441074</v>
       </c>
       <c r="T6">
-        <v>0.7115373032056954</v>
+        <v>0.7169175188149314</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>93.80842701529269</v>
+        <v>75.04674161223414</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.156656916456902</v>
+        <v>0.1562283471441419</v>
       </c>
       <c r="C7">
-        <v>68.93648083433344</v>
+        <v>68.41870835969934</v>
       </c>
       <c r="D7">
-        <v>59.01278083433344</v>
+        <v>59.21026835969933</v>
       </c>
       <c r="E7">
-        <v>3.450300000000001</v>
+        <v>4.165560000000001</v>
       </c>
       <c r="F7">
-        <v>3.576300000000001</v>
+        <v>4.291560000000001</v>
       </c>
       <c r="G7">
         <v>13.5</v>
@@ -1861,28 +1861,28 @@
         <v>13.5</v>
       </c>
       <c r="M7">
-        <v>0.17988789</v>
+        <v>0.2158654680000001</v>
       </c>
       <c r="N7">
-        <v>13.32011211</v>
+        <v>13.284134532</v>
       </c>
       <c r="O7">
-        <v>3.8628325119</v>
+        <v>3.85239901428</v>
       </c>
       <c r="P7">
-        <v>9.457279598100001</v>
+        <v>9.43173551772</v>
       </c>
       <c r="Q7">
-        <v>10.9572795981</v>
+        <v>10.93173551772</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1630223857441074</v>
+        <v>0.1639208161107893</v>
       </c>
       <c r="T7">
-        <v>0.7169175188149314</v>
+        <v>0.7224122070967043</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>75.04674161223414</v>
+        <v>62.53895134352844</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1562283471441419</v>
+        <v>0.1557997778313819</v>
       </c>
       <c r="C8">
-        <v>68.41870835969934</v>
+        <v>67.9022621157267</v>
       </c>
       <c r="D8">
-        <v>59.21026835969933</v>
+        <v>59.40908211572671</v>
       </c>
       <c r="E8">
-        <v>4.16556</v>
+        <v>4.88082</v>
       </c>
       <c r="F8">
-        <v>4.29156</v>
+        <v>5.00682</v>
       </c>
       <c r="G8">
         <v>13.5</v>
@@ -1943,28 +1943,28 @@
         <v>13.5</v>
       </c>
       <c r="M8">
-        <v>0.215865468</v>
+        <v>0.251843046</v>
       </c>
       <c r="N8">
-        <v>13.284134532</v>
+        <v>13.248156954</v>
       </c>
       <c r="O8">
-        <v>3.85239901428</v>
+        <v>3.84196551666</v>
       </c>
       <c r="P8">
-        <v>9.43173551772</v>
+        <v>9.40619143734</v>
       </c>
       <c r="Q8">
-        <v>10.93173551772</v>
+        <v>10.90619143734</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1639208161107893</v>
+        <v>0.1648385675606257</v>
       </c>
       <c r="T8">
-        <v>0.7224122070967043</v>
+        <v>0.7280250607178703</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>62.53895134352846</v>
+        <v>53.60481543731011</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1557997778313819</v>
+        <v>0.1553712085186219</v>
       </c>
       <c r="C9">
-        <v>67.90226211572673</v>
+        <v>67.38715550690971</v>
       </c>
       <c r="D9">
-        <v>59.40908211572673</v>
+        <v>59.60923550690971</v>
       </c>
       <c r="E9">
-        <v>4.880820000000001</v>
+        <v>5.596080000000001</v>
       </c>
       <c r="F9">
-        <v>5.006820000000001</v>
+        <v>5.722080000000001</v>
       </c>
       <c r="G9">
         <v>13.5</v>
@@ -2025,28 +2025,28 @@
         <v>13.5</v>
       </c>
       <c r="M9">
-        <v>0.2518430460000001</v>
+        <v>0.287820624</v>
       </c>
       <c r="N9">
-        <v>13.248156954</v>
+        <v>13.212179376</v>
       </c>
       <c r="O9">
-        <v>3.84196551666</v>
+        <v>3.83153201904</v>
       </c>
       <c r="P9">
-        <v>9.40619143734</v>
+        <v>9.380647356960001</v>
       </c>
       <c r="Q9">
-        <v>10.90619143734</v>
+        <v>10.88064735696</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1648385675606257</v>
+        <v>0.1657762701289368</v>
       </c>
       <c r="T9">
-        <v>0.7280250607178703</v>
+        <v>0.733759932896018</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>53.60481543731009</v>
+        <v>46.90421350764634</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1553712085186219</v>
+        <v>0.1549426392058618</v>
       </c>
       <c r="C10">
-        <v>67.38715550690971</v>
+        <v>66.87340211899588</v>
       </c>
       <c r="D10">
-        <v>59.60923550690971</v>
+        <v>59.81074211899589</v>
       </c>
       <c r="E10">
-        <v>5.596080000000001</v>
+        <v>6.31134</v>
       </c>
       <c r="F10">
-        <v>5.722080000000001</v>
+        <v>6.437340000000001</v>
       </c>
       <c r="G10">
         <v>13.5</v>
@@ -2107,28 +2107,28 @@
         <v>13.5</v>
       </c>
       <c r="M10">
-        <v>0.287820624</v>
+        <v>0.323798202</v>
       </c>
       <c r="N10">
-        <v>13.212179376</v>
+        <v>13.176201798</v>
       </c>
       <c r="O10">
-        <v>3.83153201904</v>
+        <v>3.82109852142</v>
       </c>
       <c r="P10">
-        <v>9.380647356960001</v>
+        <v>9.35510327658</v>
       </c>
       <c r="Q10">
-        <v>10.88064735696</v>
+        <v>10.85510327658</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1657762701289368</v>
+        <v>0.1667345815449031</v>
       </c>
       <c r="T10">
-        <v>0.733759932896018</v>
+        <v>0.7396208462209383</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>46.90421350764634</v>
+        <v>41.69263422901896</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1549426392058618</v>
+        <v>0.1545140698931018</v>
       </c>
       <c r="C11">
-        <v>66.87340211899588</v>
+        <v>66.36101572206013</v>
       </c>
       <c r="D11">
-        <v>59.81074211899589</v>
+        <v>60.01361572206014</v>
       </c>
       <c r="E11">
-        <v>6.31134</v>
+        <v>7.0266</v>
       </c>
       <c r="F11">
-        <v>6.437340000000001</v>
+        <v>7.152600000000001</v>
       </c>
       <c r="G11">
         <v>13.5</v>
@@ -2189,28 +2189,28 @@
         <v>13.5</v>
       </c>
       <c r="M11">
-        <v>0.323798202</v>
+        <v>0.35977578</v>
       </c>
       <c r="N11">
-        <v>13.176201798</v>
+        <v>13.14022422</v>
       </c>
       <c r="O11">
-        <v>3.82109852142</v>
+        <v>3.8106650238</v>
       </c>
       <c r="P11">
-        <v>9.35510327658</v>
+        <v>9.3295591962</v>
       </c>
       <c r="Q11">
-        <v>10.85510327658</v>
+        <v>10.8295591962</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1667345815449031</v>
+        <v>0.1677141887701131</v>
       </c>
       <c r="T11">
-        <v>0.7396208462209383</v>
+        <v>0.7456120020641901</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>41.69263422901896</v>
+        <v>37.52337080611708</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1545140698931018</v>
+        <v>0.1540855005803418</v>
       </c>
       <c r="C12">
-        <v>66.36101572206013</v>
+        <v>65.8500102736416</v>
       </c>
       <c r="D12">
-        <v>60.01361572206014</v>
+        <v>60.21787027364161</v>
       </c>
       <c r="E12">
-        <v>7.026600000000001</v>
+        <v>7.741860000000001</v>
       </c>
       <c r="F12">
-        <v>7.152600000000001</v>
+        <v>7.867860000000001</v>
       </c>
       <c r="G12">
         <v>13.5</v>
@@ -2271,28 +2271,28 @@
         <v>13.5</v>
       </c>
       <c r="M12">
-        <v>0.35977578</v>
+        <v>0.3957533580000001</v>
       </c>
       <c r="N12">
-        <v>13.14022422</v>
+        <v>13.104246642</v>
       </c>
       <c r="O12">
-        <v>3.8106650238</v>
+        <v>3.80023152618</v>
       </c>
       <c r="P12">
-        <v>9.3295591962</v>
+        <v>9.30401511582</v>
       </c>
       <c r="Q12">
-        <v>10.8295591962</v>
+        <v>10.80401511582</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1677141887701131</v>
+        <v>0.1687158096408334</v>
       </c>
       <c r="T12">
-        <v>0.7456120020641901</v>
+        <v>0.7517377906230207</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>37.52337080611707</v>
+        <v>34.11215527828825</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1540855005803418</v>
+        <v>0.1536569312675817</v>
       </c>
       <c r="C13">
-        <v>65.8500102736416</v>
+        <v>65.3403999219446</v>
       </c>
       <c r="D13">
-        <v>60.21787027364161</v>
+        <v>60.42351992194459</v>
       </c>
       <c r="E13">
-        <v>7.741860000000001</v>
+        <v>8.457120000000002</v>
       </c>
       <c r="F13">
-        <v>7.867860000000001</v>
+        <v>8.583120000000001</v>
       </c>
       <c r="G13">
         <v>13.5</v>
@@ -2353,28 +2353,28 @@
         <v>13.5</v>
       </c>
       <c r="M13">
-        <v>0.3957533580000001</v>
+        <v>0.431730936</v>
       </c>
       <c r="N13">
-        <v>13.104246642</v>
+        <v>13.068269064</v>
       </c>
       <c r="O13">
-        <v>3.80023152618</v>
+        <v>3.78979802856</v>
       </c>
       <c r="P13">
-        <v>9.30401511582</v>
+        <v>9.278471035440001</v>
       </c>
       <c r="Q13">
-        <v>10.80401511582</v>
+        <v>10.77847103544</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1687158096408334</v>
+        <v>0.169740194622252</v>
       </c>
       <c r="T13">
-        <v>0.7517377906230207</v>
+        <v>0.7580028016490973</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>34.11215527828825</v>
+        <v>31.26947567176423</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1536569312675817</v>
+        <v>0.1532283619548217</v>
       </c>
       <c r="C14">
-        <v>65.3403999219446</v>
+        <v>64.83219900910535</v>
       </c>
       <c r="D14">
-        <v>60.42351992194459</v>
+        <v>60.63057900910537</v>
       </c>
       <c r="E14">
-        <v>8.457120000000002</v>
+        <v>9.172380000000002</v>
       </c>
       <c r="F14">
-        <v>8.583120000000001</v>
+        <v>9.298380000000002</v>
       </c>
       <c r="G14">
         <v>13.5</v>
@@ -2435,28 +2435,28 @@
         <v>13.5</v>
       </c>
       <c r="M14">
-        <v>0.431730936</v>
+        <v>0.4677085140000001</v>
       </c>
       <c r="N14">
-        <v>13.068269064</v>
+        <v>13.032291486</v>
       </c>
       <c r="O14">
-        <v>3.78979802856</v>
+        <v>3.77936453094</v>
       </c>
       <c r="P14">
-        <v>9.278471035440001</v>
+        <v>9.252926955060001</v>
       </c>
       <c r="Q14">
-        <v>10.77847103544</v>
+        <v>10.75292695506</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.169740194622252</v>
+        <v>0.1707881286837031</v>
       </c>
       <c r="T14">
-        <v>0.7580028016490973</v>
+        <v>0.7644118359171529</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>31.26947567176423</v>
+        <v>28.86413138932082</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1532283619548217</v>
+        <v>0.1527997926420616</v>
       </c>
       <c r="C15">
-        <v>64.83219900910535</v>
+        <v>64.32542207452667</v>
       </c>
       <c r="D15">
-        <v>60.63057900910537</v>
+        <v>60.83906207452667</v>
       </c>
       <c r="E15">
-        <v>9.172380000000002</v>
+        <v>9.887640000000003</v>
       </c>
       <c r="F15">
-        <v>9.298380000000002</v>
+        <v>10.01364</v>
       </c>
       <c r="G15">
         <v>13.5</v>
@@ -2517,28 +2517,28 @@
         <v>13.5</v>
       </c>
       <c r="M15">
-        <v>0.4677085140000001</v>
+        <v>0.5036860920000001</v>
       </c>
       <c r="N15">
-        <v>13.032291486</v>
+        <v>12.996313908</v>
       </c>
       <c r="O15">
-        <v>3.77936453094</v>
+        <v>3.768931033319999</v>
       </c>
       <c r="P15">
-        <v>9.252926955060001</v>
+        <v>9.22738287468</v>
       </c>
       <c r="Q15">
-        <v>10.75292695506</v>
+        <v>10.72738287468</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1707881286837031</v>
+        <v>0.1718604333047228</v>
       </c>
       <c r="T15">
-        <v>0.7644118359171529</v>
+        <v>0.7709699174937676</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>28.86413138932082</v>
+        <v>26.80240771865505</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1527997926420616</v>
+        <v>0.1523712233293016</v>
       </c>
       <c r="C16">
-        <v>64.32542207452667</v>
+        <v>63.82008385828063</v>
       </c>
       <c r="D16">
-        <v>60.83906207452667</v>
+        <v>61.04898385828064</v>
       </c>
       <c r="E16">
-        <v>9.887640000000003</v>
+        <v>10.6029</v>
       </c>
       <c r="F16">
-        <v>10.01364</v>
+        <v>10.7289</v>
       </c>
       <c r="G16">
         <v>13.5</v>
@@ -2599,28 +2599,28 @@
         <v>13.5</v>
       </c>
       <c r="M16">
-        <v>0.5036860920000001</v>
+        <v>0.5396636700000002</v>
       </c>
       <c r="N16">
-        <v>12.996313908</v>
+        <v>12.96033633</v>
       </c>
       <c r="O16">
-        <v>3.768931033319999</v>
+        <v>3.7584975357</v>
       </c>
       <c r="P16">
-        <v>9.22738287468</v>
+        <v>9.2018387943</v>
       </c>
       <c r="Q16">
-        <v>10.72738287468</v>
+        <v>10.7018387943</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1718604333047228</v>
+        <v>0.1729579686227078</v>
       </c>
       <c r="T16">
-        <v>0.7709699174937676</v>
+        <v>0.7776823068721852</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>26.80240771865505</v>
+        <v>25.01558053741138</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1523712233293016</v>
+        <v>0.1519426540165416</v>
       </c>
       <c r="C17">
-        <v>63.82008385828063</v>
+        <v>63.31619930458312</v>
       </c>
       <c r="D17">
-        <v>61.04898385828064</v>
+        <v>61.26035930458312</v>
       </c>
       <c r="E17">
-        <v>10.6029</v>
+        <v>11.31816</v>
       </c>
       <c r="F17">
-        <v>10.7289</v>
+        <v>11.44416</v>
       </c>
       <c r="G17">
         <v>13.5</v>
@@ -2681,28 +2681,28 @@
         <v>13.5</v>
       </c>
       <c r="M17">
-        <v>0.53966367</v>
+        <v>0.575641248</v>
       </c>
       <c r="N17">
-        <v>12.96033633</v>
+        <v>12.924358752</v>
       </c>
       <c r="O17">
-        <v>3.7584975357</v>
+        <v>3.74806403808</v>
       </c>
       <c r="P17">
-        <v>9.2018387943</v>
+        <v>9.176294713920001</v>
       </c>
       <c r="Q17">
-        <v>10.7018387943</v>
+        <v>10.67629471392</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1729579686227078</v>
+        <v>0.1740816357339781</v>
       </c>
       <c r="T17">
-        <v>0.7776823068721852</v>
+        <v>0.784554515045327</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>25.01558053741138</v>
+        <v>23.45210675382317</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1519426540165416</v>
+        <v>0.1515140847037815</v>
       </c>
       <c r="C18">
-        <v>63.31619930458312</v>
+        <v>62.8137835653399</v>
       </c>
       <c r="D18">
-        <v>61.26035930458312</v>
+        <v>61.4732035653399</v>
       </c>
       <c r="E18">
-        <v>11.31816</v>
+        <v>12.03342</v>
       </c>
       <c r="F18">
-        <v>11.44416</v>
+        <v>12.15942</v>
       </c>
       <c r="G18">
         <v>13.5</v>
@@ -2763,28 +2763,28 @@
         <v>13.5</v>
       </c>
       <c r="M18">
-        <v>0.575641248</v>
+        <v>0.6116188260000001</v>
       </c>
       <c r="N18">
-        <v>12.924358752</v>
+        <v>12.888381174</v>
       </c>
       <c r="O18">
-        <v>3.74806403808</v>
+        <v>3.73763054046</v>
       </c>
       <c r="P18">
-        <v>9.176294713920001</v>
+        <v>9.15075063354</v>
       </c>
       <c r="Q18">
-        <v>10.67629471392</v>
+        <v>10.65075063354</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1740816357339781</v>
+        <v>0.1752323791611826</v>
       </c>
       <c r="T18">
-        <v>0.784554515045327</v>
+        <v>0.791592318596135</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>23.45210675382317</v>
+        <v>22.0725710624218</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1515140847037815</v>
+        <v>0.1510855153910215</v>
       </c>
       <c r="C19">
-        <v>62.8137835653399</v>
+        <v>62.31285200376727</v>
       </c>
       <c r="D19">
-        <v>61.4732035653399</v>
+        <v>61.68753200376728</v>
       </c>
       <c r="E19">
-        <v>12.03342</v>
+        <v>12.74868</v>
       </c>
       <c r="F19">
-        <v>12.15942</v>
+        <v>12.87468</v>
       </c>
       <c r="G19">
         <v>13.5</v>
@@ -2845,28 +2845,28 @@
         <v>13.5</v>
       </c>
       <c r="M19">
-        <v>0.6116188260000001</v>
+        <v>0.6475964040000002</v>
       </c>
       <c r="N19">
-        <v>12.888381174</v>
+        <v>12.852403596</v>
       </c>
       <c r="O19">
-        <v>3.73763054046</v>
+        <v>3.72719704284</v>
       </c>
       <c r="P19">
-        <v>9.15075063354</v>
+        <v>9.12520655316</v>
       </c>
       <c r="Q19">
-        <v>10.65075063354</v>
+        <v>10.62520655316</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1752323791611826</v>
+        <v>0.1764111895012457</v>
       </c>
       <c r="T19">
-        <v>0.791592318596135</v>
+        <v>0.7988017758920845</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>22.0725710624218</v>
+        <v>20.84631711450948</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1510855153910215</v>
+        <v>0.1506569460782615</v>
       </c>
       <c r="C20">
-        <v>62.31285200376728</v>
+        <v>61.81342019808876</v>
       </c>
       <c r="D20">
-        <v>61.68753200376727</v>
+        <v>61.90336019808876</v>
       </c>
       <c r="E20">
-        <v>12.74868</v>
+        <v>13.46394</v>
       </c>
       <c r="F20">
-        <v>12.87468</v>
+        <v>13.58994</v>
       </c>
       <c r="G20">
         <v>13.5</v>
@@ -2927,28 +2927,28 @@
         <v>13.5</v>
       </c>
       <c r="M20">
-        <v>0.6475964040000001</v>
+        <v>0.6835739820000001</v>
       </c>
       <c r="N20">
-        <v>12.852403596</v>
+        <v>12.816426018</v>
       </c>
       <c r="O20">
-        <v>3.72719704284</v>
+        <v>3.71676354522</v>
       </c>
       <c r="P20">
-        <v>9.12520655316</v>
+        <v>9.09966247278</v>
       </c>
       <c r="Q20">
-        <v>10.62520655316</v>
+        <v>10.59966247278</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1764111895012457</v>
+        <v>0.1776191062694586</v>
       </c>
       <c r="T20">
-        <v>0.7988017758920845</v>
+        <v>0.806189244479292</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>20.84631711450949</v>
+        <v>19.7491425295353</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1506569460782615</v>
+        <v>0.1502283767655015</v>
       </c>
       <c r="C21">
-        <v>61.81342019808876</v>
+        <v>61.31550394530943</v>
       </c>
       <c r="D21">
-        <v>61.90336019808876</v>
+        <v>62.12070394530942</v>
       </c>
       <c r="E21">
-        <v>13.46394</v>
+        <v>14.1792</v>
       </c>
       <c r="F21">
-        <v>13.58994</v>
+        <v>14.3052</v>
       </c>
       <c r="G21">
         <v>13.5</v>
@@ -3009,28 +3009,28 @@
         <v>13.5</v>
       </c>
       <c r="M21">
-        <v>0.6835739820000001</v>
+        <v>0.7195515600000001</v>
       </c>
       <c r="N21">
-        <v>12.816426018</v>
+        <v>12.78044844</v>
       </c>
       <c r="O21">
-        <v>3.71676354522</v>
+        <v>3.7063300476</v>
       </c>
       <c r="P21">
-        <v>9.09966247278</v>
+        <v>9.074118392400001</v>
       </c>
       <c r="Q21">
-        <v>10.59966247278</v>
+        <v>10.5741183924</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1776191062694586</v>
+        <v>0.1788572209568768</v>
       </c>
       <c r="T21">
-        <v>0.806189244479292</v>
+        <v>0.8137613997811798</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>19.7491425295353</v>
+        <v>18.76168540305854</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1502283767655015</v>
+        <v>0.1497998074527414</v>
       </c>
       <c r="C22">
-        <v>61.31550394530943</v>
+        <v>60.81911926507036</v>
       </c>
       <c r="D22">
-        <v>62.12070394530942</v>
+        <v>62.33957926507036</v>
       </c>
       <c r="E22">
-        <v>14.1792</v>
+        <v>14.89446</v>
       </c>
       <c r="F22">
-        <v>14.3052</v>
+        <v>15.02046</v>
       </c>
       <c r="G22">
         <v>13.5</v>
@@ -3091,28 +3091,28 @@
         <v>13.5</v>
       </c>
       <c r="M22">
-        <v>0.7195515600000001</v>
+        <v>0.7555291380000001</v>
       </c>
       <c r="N22">
-        <v>12.78044844</v>
+        <v>12.744470862</v>
       </c>
       <c r="O22">
-        <v>3.7063300476</v>
+        <v>3.69589654998</v>
       </c>
       <c r="P22">
-        <v>9.074118392400001</v>
+        <v>9.048574312020001</v>
       </c>
       <c r="Q22">
-        <v>10.5741183924</v>
+        <v>10.54857431202</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1788572209568768</v>
+        <v>0.1801266803199258</v>
       </c>
       <c r="T22">
-        <v>0.8137613997811798</v>
+        <v>0.8215252552172925</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>18.76168540305854</v>
+        <v>17.8682718124367</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1497998074527414</v>
+        <v>0.1493712381399813</v>
       </c>
       <c r="C23">
-        <v>60.81911926507036</v>
+        <v>60.32428240358443</v>
       </c>
       <c r="D23">
-        <v>62.33957926507036</v>
+        <v>62.56000240358443</v>
       </c>
       <c r="E23">
-        <v>14.89446</v>
+        <v>15.60972</v>
       </c>
       <c r="F23">
-        <v>15.02046</v>
+        <v>15.73572</v>
       </c>
       <c r="G23">
         <v>13.5</v>
@@ -3173,28 +3173,28 @@
         <v>13.5</v>
       </c>
       <c r="M23">
-        <v>0.7555291380000001</v>
+        <v>0.7915067160000001</v>
       </c>
       <c r="N23">
-        <v>12.744470862</v>
+        <v>12.708493284</v>
       </c>
       <c r="O23">
-        <v>3.69589654998</v>
+        <v>3.685463052359999</v>
       </c>
       <c r="P23">
-        <v>9.048574312020001</v>
+        <v>9.02303023164</v>
       </c>
       <c r="Q23">
-        <v>10.54857431202</v>
+        <v>10.52303023164</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1801266803199258</v>
+        <v>0.181428689923053</v>
       </c>
       <c r="T23">
-        <v>0.8215252552172925</v>
+        <v>0.8294881838697158</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>17.8682718124367</v>
+        <v>17.05607763914412</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1493712381399813</v>
+        <v>0.1489426688272213</v>
       </c>
       <c r="C24">
-        <v>60.32428240358443</v>
+        <v>59.83100983765631</v>
       </c>
       <c r="D24">
-        <v>62.56000240358443</v>
+        <v>62.7819898376563</v>
       </c>
       <c r="E24">
-        <v>15.60972</v>
+        <v>16.32498</v>
       </c>
       <c r="F24">
-        <v>15.73572</v>
+        <v>16.45098</v>
       </c>
       <c r="G24">
         <v>13.5</v>
@@ -3255,28 +3255,28 @@
         <v>13.5</v>
       </c>
       <c r="M24">
-        <v>0.7915067160000001</v>
+        <v>0.8274842940000002</v>
       </c>
       <c r="N24">
-        <v>12.708493284</v>
+        <v>12.672515706</v>
       </c>
       <c r="O24">
-        <v>3.685463052359999</v>
+        <v>3.67502955474</v>
       </c>
       <c r="P24">
-        <v>9.02303023164</v>
+        <v>8.99748615126</v>
       </c>
       <c r="Q24">
-        <v>10.52303023164</v>
+        <v>10.49748615126</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.181428689923053</v>
+        <v>0.1827645179574303</v>
       </c>
       <c r="T24">
-        <v>0.8294881838697158</v>
+        <v>0.8376579418377865</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>17.05607763914412</v>
+        <v>16.31450904613786</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1489426688272213</v>
+        <v>0.1485140995144613</v>
       </c>
       <c r="C25">
-        <v>59.83100983765631</v>
+        <v>59.3393182787882</v>
       </c>
       <c r="D25">
-        <v>62.7819898376563</v>
+        <v>63.0055582787882</v>
       </c>
       <c r="E25">
-        <v>16.32498</v>
+        <v>17.04024</v>
       </c>
       <c r="F25">
-        <v>16.45098</v>
+        <v>17.16624000000001</v>
       </c>
       <c r="G25">
         <v>13.5</v>
@@ -3337,28 +3337,28 @@
         <v>13.5</v>
       </c>
       <c r="M25">
-        <v>0.8274842940000002</v>
+        <v>0.8634618720000002</v>
       </c>
       <c r="N25">
-        <v>12.672515706</v>
+        <v>12.636538128</v>
       </c>
       <c r="O25">
-        <v>3.67502955474</v>
+        <v>3.66459605712</v>
       </c>
       <c r="P25">
-        <v>8.99748615126</v>
+        <v>8.971942070880001</v>
       </c>
       <c r="Q25">
-        <v>10.49748615126</v>
+        <v>10.47194207088</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1827645179574303</v>
+        <v>0.1841354993611333</v>
       </c>
       <c r="T25">
-        <v>0.8376579418377865</v>
+        <v>0.8460426934365959</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>16.31450904613786</v>
+        <v>15.63473783588211</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1485140995144613</v>
+        <v>0.1480855302017013</v>
       </c>
       <c r="C26">
-        <v>59.3393182787882</v>
+        <v>58.84922467737339</v>
       </c>
       <c r="D26">
-        <v>63.0055582787882</v>
+        <v>63.23072467737339</v>
       </c>
       <c r="E26">
-        <v>17.04024</v>
+        <v>17.7555</v>
       </c>
       <c r="F26">
-        <v>17.16624</v>
+        <v>17.8815</v>
       </c>
       <c r="G26">
         <v>13.5</v>
@@ -3419,28 +3419,28 @@
         <v>13.5</v>
       </c>
       <c r="M26">
-        <v>0.863461872</v>
+        <v>0.8994394500000001</v>
       </c>
       <c r="N26">
-        <v>12.636538128</v>
+        <v>12.60056055</v>
       </c>
       <c r="O26">
-        <v>3.66459605712</v>
+        <v>3.6541625595</v>
       </c>
       <c r="P26">
-        <v>8.971942070880001</v>
+        <v>8.9463979905</v>
       </c>
       <c r="Q26">
-        <v>10.47194207088</v>
+        <v>10.4463979905</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1841354993611333</v>
+        <v>0.185543040268935</v>
       </c>
       <c r="T26">
-        <v>0.8460426934365959</v>
+        <v>0.8546510384113735</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>15.63473783588211</v>
+        <v>15.00934832244683</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1480855302017013</v>
+        <v>0.1476569608889412</v>
       </c>
       <c r="C27">
-        <v>58.84922467737339</v>
+        <v>58.36074622698055</v>
       </c>
       <c r="D27">
-        <v>63.23072467737339</v>
+        <v>63.45750622698056</v>
       </c>
       <c r="E27">
-        <v>17.7555</v>
+        <v>18.47076</v>
       </c>
       <c r="F27">
-        <v>17.8815</v>
+        <v>18.59676</v>
       </c>
       <c r="G27">
         <v>13.5</v>
@@ -3501,28 +3501,28 @@
         <v>13.5</v>
       </c>
       <c r="M27">
-        <v>0.8994394500000001</v>
+        <v>0.9354170280000002</v>
       </c>
       <c r="N27">
-        <v>12.60056055</v>
+        <v>12.564582972</v>
       </c>
       <c r="O27">
-        <v>3.6541625595</v>
+        <v>3.64372906188</v>
       </c>
       <c r="P27">
-        <v>8.9463979905</v>
+        <v>8.92085391012</v>
       </c>
       <c r="Q27">
-        <v>10.4463979905</v>
+        <v>10.42085391012</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.185543040268935</v>
+        <v>0.1869886228228935</v>
       </c>
       <c r="T27">
-        <v>0.8546510384113735</v>
+        <v>0.8634920413584424</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>15.00934832244683</v>
+        <v>14.43206569466041</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1476569608889412</v>
+        <v>0.1472283915761812</v>
       </c>
       <c r="C28">
-        <v>58.36074622698055</v>
+        <v>57.87390036873005</v>
       </c>
       <c r="D28">
-        <v>63.45750622698056</v>
+        <v>63.68592036873005</v>
       </c>
       <c r="E28">
-        <v>18.47076</v>
+        <v>19.18602</v>
       </c>
       <c r="F28">
-        <v>18.59676</v>
+        <v>19.31202</v>
       </c>
       <c r="G28">
         <v>13.5</v>
@@ -3583,28 +3583,28 @@
         <v>13.5</v>
       </c>
       <c r="M28">
-        <v>0.9354170280000002</v>
+        <v>0.9713946060000002</v>
       </c>
       <c r="N28">
-        <v>12.564582972</v>
+        <v>12.528605394</v>
       </c>
       <c r="O28">
-        <v>3.64372906188</v>
+        <v>3.63329556426</v>
       </c>
       <c r="P28">
-        <v>8.92085391012</v>
+        <v>8.89530982974</v>
       </c>
       <c r="Q28">
-        <v>10.42085391012</v>
+        <v>10.39530982974</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1869886228228935</v>
+        <v>0.1884738103783304</v>
       </c>
       <c r="T28">
-        <v>0.8634920413584424</v>
+        <v>0.8725752635643351</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>14.43206569466041</v>
+        <v>13.89754474300632</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1472283915761812</v>
+        <v>0.1467998222634211</v>
       </c>
       <c r="C29">
-        <v>57.87390036873005</v>
+        <v>57.38870479576529</v>
       </c>
       <c r="D29">
-        <v>63.68592036873005</v>
+        <v>63.91598479576529</v>
       </c>
       <c r="E29">
-        <v>19.18602</v>
+        <v>19.90128</v>
       </c>
       <c r="F29">
-        <v>19.31202</v>
+        <v>20.02728</v>
       </c>
       <c r="G29">
         <v>13.5</v>
@@ -3665,28 +3665,28 @@
         <v>13.5</v>
       </c>
       <c r="M29">
-        <v>0.9713946060000002</v>
+        <v>1.007372184</v>
       </c>
       <c r="N29">
-        <v>12.528605394</v>
+        <v>12.492627816</v>
       </c>
       <c r="O29">
-        <v>3.63329556426</v>
+        <v>3.622862066639999</v>
       </c>
       <c r="P29">
-        <v>8.89530982974</v>
+        <v>8.869765749359999</v>
       </c>
       <c r="Q29">
-        <v>10.39530982974</v>
+        <v>10.36976574936</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1884738103783304</v>
+        <v>0.1900002531436405</v>
       </c>
       <c r="T29">
-        <v>0.8725752635643351</v>
+        <v>0.8819107974981694</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>13.89754474300632</v>
+        <v>13.40120385932752</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1467998222634211</v>
+        <v>0.1463712529506611</v>
       </c>
       <c r="C30">
-        <v>57.38870479576529</v>
+        <v>56.90517745782164</v>
       </c>
       <c r="D30">
-        <v>63.91598479576529</v>
+        <v>64.14771745782164</v>
       </c>
       <c r="E30">
-        <v>19.90128</v>
+        <v>20.61654</v>
       </c>
       <c r="F30">
-        <v>20.02728</v>
+        <v>20.74254000000001</v>
       </c>
       <c r="G30">
         <v>13.5</v>
@@ -3747,28 +3747,28 @@
         <v>13.5</v>
       </c>
       <c r="M30">
-        <v>1.007372184</v>
+        <v>1.043349762</v>
       </c>
       <c r="N30">
-        <v>12.492627816</v>
+        <v>12.456650238</v>
       </c>
       <c r="O30">
-        <v>3.622862066639999</v>
+        <v>3.61242856902</v>
       </c>
       <c r="P30">
-        <v>8.869765749359999</v>
+        <v>8.844221668980001</v>
       </c>
       <c r="Q30">
-        <v>10.36976574936</v>
+        <v>10.34422166898</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1900002531436405</v>
+        <v>0.1915696942967058</v>
       </c>
       <c r="T30">
-        <v>0.8819107974981694</v>
+        <v>0.8915093042188721</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>13.40120385932752</v>
+        <v>12.93909338141968</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1463712529506611</v>
+        <v>0.1462621836379011</v>
       </c>
       <c r="C31">
-        <v>56.90517745782164</v>
+        <v>56.24916105044764</v>
       </c>
       <c r="D31">
-        <v>64.14771745782164</v>
+        <v>64.20696105044765</v>
       </c>
       <c r="E31">
-        <v>20.61654</v>
+        <v>21.3318</v>
       </c>
       <c r="F31">
-        <v>20.74254</v>
+        <v>21.4578</v>
       </c>
       <c r="G31">
         <v>13.5</v>
@@ -3829,45 +3829,45 @@
         <v>13.5</v>
       </c>
       <c r="M31">
-        <v>1.043349762</v>
+        <v>1.11151404</v>
       </c>
       <c r="N31">
-        <v>12.456650238</v>
+        <v>12.38848596</v>
       </c>
       <c r="O31">
-        <v>3.61242856902</v>
+        <v>3.5926609284</v>
       </c>
       <c r="P31">
-        <v>8.844221668980001</v>
+        <v>8.7958250316</v>
       </c>
       <c r="Q31">
-        <v>10.34422166898</v>
+        <v>10.2958250316</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1915696942967058</v>
+        <v>0.193183976625573</v>
       </c>
       <c r="T31">
-        <v>0.8915093042188721</v>
+        <v>0.9013820539887377</v>
       </c>
       <c r="U31">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V31">
         <v>0.29</v>
       </c>
       <c r="W31">
-        <v>0.03571299999999999</v>
+        <v>0.036778</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y31">
-        <v>12.93909338141968</v>
+        <v>12.14559556980495</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1462621836379011</v>
+        <v>0.145844264325141</v>
       </c>
       <c r="C32">
-        <v>56.24916105044764</v>
+        <v>55.76192042212405</v>
       </c>
       <c r="D32">
-        <v>64.20696105044765</v>
+        <v>64.43498042212406</v>
       </c>
       <c r="E32">
-        <v>21.3318</v>
+        <v>22.04706</v>
       </c>
       <c r="F32">
-        <v>21.4578</v>
+        <v>22.17306</v>
       </c>
       <c r="G32">
         <v>13.5</v>
@@ -3911,28 +3911,28 @@
         <v>13.5</v>
       </c>
       <c r="M32">
-        <v>1.11151404</v>
+        <v>1.148564508</v>
       </c>
       <c r="N32">
-        <v>12.38848596</v>
+        <v>12.351435492</v>
       </c>
       <c r="O32">
-        <v>3.5926609284</v>
+        <v>3.58191629268</v>
       </c>
       <c r="P32">
-        <v>8.7958250316</v>
+        <v>8.769519199320001</v>
       </c>
       <c r="Q32">
-        <v>10.2958250316</v>
+        <v>10.26951919932</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.193183976625573</v>
+        <v>0.1948450497465812</v>
       </c>
       <c r="T32">
-        <v>0.9013820539887377</v>
+        <v>0.9115409704185995</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>12.14559556980495</v>
+        <v>11.75380216432737</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.145844264325141</v>
+        <v>0.145426345012381</v>
       </c>
       <c r="C33">
-        <v>55.76192042212405</v>
+        <v>55.27630510464482</v>
       </c>
       <c r="D33">
-        <v>64.43498042212406</v>
+        <v>64.66462510464483</v>
       </c>
       <c r="E33">
-        <v>22.04706</v>
+        <v>22.76232</v>
       </c>
       <c r="F33">
-        <v>22.17306</v>
+        <v>22.88832</v>
       </c>
       <c r="G33">
         <v>13.5</v>
@@ -3993,28 +3993,28 @@
         <v>13.5</v>
       </c>
       <c r="M33">
-        <v>1.148564508</v>
+        <v>1.185614976</v>
       </c>
       <c r="N33">
-        <v>12.351435492</v>
+        <v>12.314385024</v>
       </c>
       <c r="O33">
-        <v>3.58191629268</v>
+        <v>3.57117165696</v>
       </c>
       <c r="P33">
-        <v>8.769519199320001</v>
+        <v>8.743213367039999</v>
       </c>
       <c r="Q33">
-        <v>10.26951919932</v>
+        <v>10.24321336704</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1948450497465812</v>
+        <v>0.1965549779593838</v>
       </c>
       <c r="T33">
-        <v>0.9115409704185995</v>
+        <v>0.9219986785081633</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.75380216432737</v>
+        <v>11.38649584669214</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.145426345012381</v>
+        <v>0.145008425699621</v>
       </c>
       <c r="C34">
-        <v>55.27630510464482</v>
+        <v>54.79233253786853</v>
       </c>
       <c r="D34">
-        <v>64.66462510464483</v>
+        <v>64.89591253786854</v>
       </c>
       <c r="E34">
-        <v>22.76232</v>
+        <v>23.47758</v>
       </c>
       <c r="F34">
-        <v>22.88832</v>
+        <v>23.60358</v>
       </c>
       <c r="G34">
         <v>13.5</v>
@@ -4075,28 +4075,28 @@
         <v>13.5</v>
       </c>
       <c r="M34">
-        <v>1.185614976</v>
+        <v>1.222665444</v>
       </c>
       <c r="N34">
-        <v>12.314385024</v>
+        <v>12.277334556</v>
       </c>
       <c r="O34">
-        <v>3.57117165696</v>
+        <v>3.56042702124</v>
       </c>
       <c r="P34">
-        <v>8.743213367039999</v>
+        <v>8.716907534760001</v>
       </c>
       <c r="Q34">
-        <v>10.24321336704</v>
+        <v>10.21690753476</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1965549779593838</v>
+        <v>0.1983159488054044</v>
       </c>
       <c r="T34">
-        <v>0.9219986785081633</v>
+        <v>0.9327685569884601</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>11.38649584669214</v>
+        <v>11.0414505180045</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.145008425699621</v>
+        <v>0.1445905063868609</v>
       </c>
       <c r="C35">
-        <v>54.79233253786853</v>
+        <v>54.31002041205964</v>
       </c>
       <c r="D35">
-        <v>64.89591253786854</v>
+        <v>65.12886041205965</v>
       </c>
       <c r="E35">
-        <v>23.47758</v>
+        <v>24.19284</v>
       </c>
       <c r="F35">
-        <v>23.60358</v>
+        <v>24.31884000000001</v>
       </c>
       <c r="G35">
         <v>13.5</v>
@@ -4157,28 +4157,28 @@
         <v>13.5</v>
       </c>
       <c r="M35">
-        <v>1.222665444</v>
+        <v>1.259715912</v>
       </c>
       <c r="N35">
-        <v>12.277334556</v>
+        <v>12.240284088</v>
       </c>
       <c r="O35">
-        <v>3.56042702124</v>
+        <v>3.54968238552</v>
       </c>
       <c r="P35">
-        <v>8.716907534760001</v>
+        <v>8.690601702479999</v>
       </c>
       <c r="Q35">
-        <v>10.21690753476</v>
+        <v>10.19060170248</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1983159488054044</v>
+        <v>0.2001302824043348</v>
       </c>
       <c r="T35">
-        <v>0.9327685569884601</v>
+        <v>0.9438647954227053</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.0414505180045</v>
+        <v>10.7167019733573</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1445905063868609</v>
+        <v>0.1441725870741009</v>
       </c>
       <c r="C36">
-        <v>54.31002041205964</v>
+        <v>53.82938667239873</v>
       </c>
       <c r="D36">
-        <v>65.12886041205965</v>
+        <v>65.36348667239874</v>
       </c>
       <c r="E36">
-        <v>24.19284</v>
+        <v>24.9081</v>
       </c>
       <c r="F36">
-        <v>24.31884000000001</v>
+        <v>25.03410000000001</v>
       </c>
       <c r="G36">
         <v>13.5</v>
@@ -4239,28 +4239,28 @@
         <v>13.5</v>
       </c>
       <c r="M36">
-        <v>1.259715912</v>
+        <v>1.29676638</v>
       </c>
       <c r="N36">
-        <v>12.240284088</v>
+        <v>12.20323362</v>
       </c>
       <c r="O36">
-        <v>3.54968238552</v>
+        <v>3.5389377498</v>
       </c>
       <c r="P36">
-        <v>8.690601702479999</v>
+        <v>8.6642958702</v>
       </c>
       <c r="Q36">
-        <v>10.19060170248</v>
+        <v>10.1642958702</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2001302824043348</v>
+        <v>0.2020004416524629</v>
       </c>
       <c r="T36">
-        <v>0.9438647954227053</v>
+        <v>0.9553024565780044</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.7167019733573</v>
+        <v>10.41051048840424</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1441725870741009</v>
+        <v>0.1437546677613408</v>
       </c>
       <c r="C37">
-        <v>53.82938667239873</v>
+        <v>53.35044952359095</v>
       </c>
       <c r="D37">
-        <v>65.36348667239874</v>
+        <v>65.59980952359096</v>
       </c>
       <c r="E37">
-        <v>24.9081</v>
+        <v>25.62336000000001</v>
       </c>
       <c r="F37">
-        <v>25.03410000000001</v>
+        <v>25.74936000000001</v>
       </c>
       <c r="G37">
         <v>13.5</v>
@@ -4321,28 +4321,28 @@
         <v>13.5</v>
       </c>
       <c r="M37">
-        <v>1.29676638</v>
+        <v>1.333816848</v>
       </c>
       <c r="N37">
-        <v>12.20323362</v>
+        <v>12.166183152</v>
       </c>
       <c r="O37">
-        <v>3.5389377498</v>
+        <v>3.52819311408</v>
       </c>
       <c r="P37">
-        <v>8.6642958702</v>
+        <v>8.63799003792</v>
       </c>
       <c r="Q37">
-        <v>10.1642958702</v>
+        <v>10.13799003792</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2020004416524629</v>
+        <v>0.2039290433770951</v>
       </c>
       <c r="T37">
-        <v>0.9553024565780044</v>
+        <v>0.9670975446444063</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>10.41051048840424</v>
+        <v>10.12132964150412</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1437546677613409</v>
+        <v>0.1433367484485808</v>
       </c>
       <c r="C38">
-        <v>53.35044952359095</v>
+        <v>52.87322743457447</v>
       </c>
       <c r="D38">
-        <v>65.59980952359095</v>
+        <v>65.83784743457447</v>
       </c>
       <c r="E38">
-        <v>25.62336</v>
+        <v>26.33862</v>
       </c>
       <c r="F38">
-        <v>25.74936</v>
+        <v>26.46462</v>
       </c>
       <c r="G38">
         <v>13.5</v>
@@ -4403,28 +4403,28 @@
         <v>13.5</v>
       </c>
       <c r="M38">
-        <v>1.333816848</v>
+        <v>1.370867316</v>
       </c>
       <c r="N38">
-        <v>12.166183152</v>
+        <v>12.129132684</v>
       </c>
       <c r="O38">
-        <v>3.52819311408</v>
+        <v>3.51744847836</v>
       </c>
       <c r="P38">
-        <v>8.63799003792</v>
+        <v>8.61168420564</v>
       </c>
       <c r="Q38">
-        <v>10.13799003792</v>
+        <v>10.11168420564</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2039290433770951</v>
+        <v>0.2059188705533029</v>
       </c>
       <c r="T38">
-        <v>0.9670975446444063</v>
+        <v>0.9792670799510116</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.12132964150412</v>
+        <v>9.84778019173374</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1433367484485808</v>
+        <v>0.1433774891358208</v>
       </c>
       <c r="C39">
-        <v>52.87322743457447</v>
+        <v>52.13468644232884</v>
       </c>
       <c r="D39">
-        <v>65.83784743457447</v>
+        <v>65.81456644232884</v>
       </c>
       <c r="E39">
-        <v>26.33862</v>
+        <v>27.05388</v>
       </c>
       <c r="F39">
-        <v>26.46462</v>
+        <v>27.17988</v>
       </c>
       <c r="G39">
         <v>13.5</v>
@@ -4485,45 +4485,45 @@
         <v>13.5</v>
       </c>
       <c r="M39">
-        <v>1.370867316</v>
+        <v>1.45412358</v>
       </c>
       <c r="N39">
-        <v>12.129132684</v>
+        <v>12.04587642</v>
       </c>
       <c r="O39">
-        <v>3.51744847836</v>
+        <v>3.493304161799999</v>
       </c>
       <c r="P39">
-        <v>8.61168420564</v>
+        <v>8.5525722582</v>
       </c>
       <c r="Q39">
-        <v>10.11168420564</v>
+        <v>10.0525722582</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2059188705533029</v>
+        <v>0.2079728857029367</v>
       </c>
       <c r="T39">
-        <v>0.9792670799510116</v>
+        <v>0.9918291809126686</v>
       </c>
       <c r="U39">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V39">
         <v>0.29</v>
       </c>
       <c r="W39">
-        <v>0.036778</v>
+        <v>0.037985</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>9.84778019173374</v>
+        <v>9.283942703136686</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1433774891358208</v>
+        <v>0.1429716398230607</v>
       </c>
       <c r="C40">
-        <v>52.13468644232884</v>
+        <v>51.65208385546016</v>
       </c>
       <c r="D40">
-        <v>65.81456644232884</v>
+        <v>66.04722385546016</v>
       </c>
       <c r="E40">
-        <v>27.05388</v>
+        <v>27.76914</v>
       </c>
       <c r="F40">
-        <v>27.17988</v>
+        <v>27.89514</v>
       </c>
       <c r="G40">
         <v>13.5</v>
@@ -4567,28 +4567,28 @@
         <v>13.5</v>
       </c>
       <c r="M40">
-        <v>1.45412358</v>
+        <v>1.49238999</v>
       </c>
       <c r="N40">
-        <v>12.04587642</v>
+        <v>12.00761001</v>
       </c>
       <c r="O40">
-        <v>3.493304161799999</v>
+        <v>3.4822069029</v>
       </c>
       <c r="P40">
-        <v>8.5525722582</v>
+        <v>8.525403107100001</v>
       </c>
       <c r="Q40">
-        <v>10.0525722582</v>
+        <v>10.0254031071</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2079728857029367</v>
+        <v>0.210094245611575</v>
       </c>
       <c r="T40">
-        <v>0.9918291809126686</v>
+        <v>1.004803154037003</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>9.283942703136686</v>
+        <v>9.045892890235748</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1429716398230607</v>
+        <v>0.1425657905103007</v>
       </c>
       <c r="C41">
-        <v>51.65208385546016</v>
+        <v>51.17113201260565</v>
       </c>
       <c r="D41">
-        <v>66.04722385546016</v>
+        <v>66.28153201260565</v>
       </c>
       <c r="E41">
-        <v>27.76914</v>
+        <v>28.4844</v>
       </c>
       <c r="F41">
-        <v>27.89514</v>
+        <v>28.61040000000001</v>
       </c>
       <c r="G41">
         <v>13.5</v>
@@ -4649,28 +4649,28 @@
         <v>13.5</v>
       </c>
       <c r="M41">
-        <v>1.49238999</v>
+        <v>1.5306564</v>
       </c>
       <c r="N41">
-        <v>12.00761001</v>
+        <v>11.9693436</v>
       </c>
       <c r="O41">
-        <v>3.4822069029</v>
+        <v>3.471109644</v>
       </c>
       <c r="P41">
-        <v>8.525403107100001</v>
+        <v>8.498233956</v>
       </c>
       <c r="Q41">
-        <v>10.0254031071</v>
+        <v>9.998233956</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.210094245611575</v>
+        <v>0.2122863175171678</v>
       </c>
       <c r="T41">
-        <v>1.004803154037003</v>
+        <v>1.018209592932148</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>9.045892890235748</v>
+        <v>8.819745567979854</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1425657905103007</v>
+        <v>0.1421599411975407</v>
       </c>
       <c r="C42">
-        <v>51.17113201260565</v>
+        <v>50.69184854477822</v>
       </c>
       <c r="D42">
-        <v>66.28153201260565</v>
+        <v>66.51750854477822</v>
       </c>
       <c r="E42">
-        <v>28.4844</v>
+        <v>29.19966000000001</v>
       </c>
       <c r="F42">
-        <v>28.61040000000001</v>
+        <v>29.32566000000001</v>
       </c>
       <c r="G42">
         <v>13.5</v>
@@ -4731,28 +4731,28 @@
         <v>13.5</v>
       </c>
       <c r="M42">
-        <v>1.5306564</v>
+        <v>1.56892281</v>
       </c>
       <c r="N42">
-        <v>11.9693436</v>
+        <v>11.93107719</v>
       </c>
       <c r="O42">
-        <v>3.471109644</v>
+        <v>3.4600123851</v>
       </c>
       <c r="P42">
-        <v>8.498233956</v>
+        <v>8.471064804899999</v>
       </c>
       <c r="Q42">
-        <v>9.998233956</v>
+        <v>9.971064804899999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2122863175171678</v>
+        <v>0.2145526969449842</v>
       </c>
       <c r="T42">
-        <v>1.018209592932148</v>
+        <v>1.032070487383062</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.819745567979854</v>
+        <v>8.604629822419369</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1421599411975407</v>
+        <v>0.1417540918847806</v>
       </c>
       <c r="C43">
-        <v>50.69184854477822</v>
+        <v>50.21425133496866</v>
       </c>
       <c r="D43">
-        <v>66.51750854477822</v>
+        <v>66.75517133496867</v>
       </c>
       <c r="E43">
-        <v>29.19966000000001</v>
+        <v>29.91492000000001</v>
       </c>
       <c r="F43">
-        <v>29.32566000000001</v>
+        <v>30.04092000000001</v>
       </c>
       <c r="G43">
         <v>13.5</v>
@@ -4813,28 +4813,28 @@
         <v>13.5</v>
       </c>
       <c r="M43">
-        <v>1.56892281</v>
+        <v>1.60718922</v>
       </c>
       <c r="N43">
-        <v>11.93107719</v>
+        <v>11.89281078</v>
       </c>
       <c r="O43">
-        <v>3.4600123851</v>
+        <v>3.4489151262</v>
       </c>
       <c r="P43">
-        <v>8.471064804899999</v>
+        <v>8.4438956538</v>
       </c>
       <c r="Q43">
-        <v>9.971064804899999</v>
+        <v>9.9438956538</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2145526969449842</v>
+        <v>0.2168972273875528</v>
       </c>
       <c r="T43">
-        <v>1.032070487383062</v>
+        <v>1.046409343711592</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.604629822419369</v>
+        <v>8.399757683790336</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1417540918847806</v>
+        <v>0.1413482425720206</v>
       </c>
       <c r="C44">
-        <v>50.21425133496864</v>
+        <v>49.73835852266325</v>
       </c>
       <c r="D44">
-        <v>66.75517133496864</v>
+        <v>66.99453852266325</v>
       </c>
       <c r="E44">
-        <v>29.91492</v>
+        <v>30.63018</v>
       </c>
       <c r="F44">
-        <v>30.04092</v>
+        <v>30.75618</v>
       </c>
       <c r="G44">
         <v>13.5</v>
@@ -4895,28 +4895,28 @@
         <v>13.5</v>
       </c>
       <c r="M44">
-        <v>1.60718922</v>
+        <v>1.64545563</v>
       </c>
       <c r="N44">
-        <v>11.89281078</v>
+        <v>11.85454437</v>
       </c>
       <c r="O44">
-        <v>3.4489151262</v>
+        <v>3.4378178673</v>
       </c>
       <c r="P44">
-        <v>8.4438956538</v>
+        <v>8.4167265027</v>
       </c>
       <c r="Q44">
-        <v>9.9438956538</v>
+        <v>9.9167265027</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2168972273875528</v>
+        <v>0.2193240220561765</v>
       </c>
       <c r="T44">
-        <v>1.046409343711592</v>
+        <v>1.061251317806037</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.399757683790337</v>
+        <v>8.204414481841724</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1413482425720206</v>
+        <v>0.1409423932592606</v>
       </c>
       <c r="C45">
-        <v>49.73835852266325</v>
+        <v>49.26418850845911</v>
       </c>
       <c r="D45">
-        <v>66.99453852266325</v>
+        <v>67.23562850845911</v>
       </c>
       <c r="E45">
-        <v>30.63018</v>
+        <v>31.34544</v>
       </c>
       <c r="F45">
-        <v>30.75618</v>
+        <v>31.47144</v>
       </c>
       <c r="G45">
         <v>13.5</v>
@@ -4977,28 +4977,28 @@
         <v>13.5</v>
       </c>
       <c r="M45">
-        <v>1.64545563</v>
+        <v>1.68372204</v>
       </c>
       <c r="N45">
-        <v>11.85454437</v>
+        <v>11.81627796</v>
       </c>
       <c r="O45">
-        <v>3.4378178673</v>
+        <v>3.4267206084</v>
       </c>
       <c r="P45">
-        <v>8.4167265027</v>
+        <v>8.389557351600001</v>
       </c>
       <c r="Q45">
-        <v>9.9167265027</v>
+        <v>9.889557351600001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2193240220561765</v>
+        <v>0.2218374879629653</v>
       </c>
       <c r="T45">
-        <v>1.061251317806037</v>
+        <v>1.076623362403854</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.204414481841724</v>
+        <v>8.017950516345323</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1409423932592606</v>
+        <v>0.1405365439465005</v>
       </c>
       <c r="C46">
-        <v>49.26418850845911</v>
+        <v>48.79175995877932</v>
       </c>
       <c r="D46">
-        <v>67.23562850845911</v>
+        <v>67.47845995877933</v>
       </c>
       <c r="E46">
-        <v>31.34544</v>
+        <v>32.06070000000001</v>
       </c>
       <c r="F46">
-        <v>31.47144</v>
+        <v>32.18670000000001</v>
       </c>
       <c r="G46">
         <v>13.5</v>
@@ -5059,28 +5059,28 @@
         <v>13.5</v>
       </c>
       <c r="M46">
-        <v>1.68372204</v>
+        <v>1.72198845</v>
       </c>
       <c r="N46">
-        <v>11.81627796</v>
+        <v>11.77801155</v>
       </c>
       <c r="O46">
-        <v>3.4267206084</v>
+        <v>3.415623349499999</v>
       </c>
       <c r="P46">
-        <v>8.389557351600001</v>
+        <v>8.3623882005</v>
       </c>
       <c r="Q46">
-        <v>9.889557351600001</v>
+        <v>9.8623882005</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2218374879629653</v>
+        <v>0.224442352630001</v>
       </c>
       <c r="T46">
-        <v>1.076623362403854</v>
+        <v>1.092554390441592</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.017950516345323</v>
+        <v>7.839773838204313</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1405365439465005</v>
+        <v>0.1401306946337405</v>
       </c>
       <c r="C47">
-        <v>48.79175995877932</v>
+        <v>48.32109181069054</v>
       </c>
       <c r="D47">
-        <v>67.47845995877933</v>
+        <v>67.72305181069055</v>
       </c>
       <c r="E47">
-        <v>32.06070000000001</v>
+        <v>32.77596000000001</v>
       </c>
       <c r="F47">
-        <v>32.18670000000001</v>
+        <v>32.90196000000001</v>
       </c>
       <c r="G47">
         <v>13.5</v>
@@ -5141,28 +5141,28 @@
         <v>13.5</v>
       </c>
       <c r="M47">
-        <v>1.72198845</v>
+        <v>1.760254860000001</v>
       </c>
       <c r="N47">
-        <v>11.77801155</v>
+        <v>11.73974514</v>
       </c>
       <c r="O47">
-        <v>3.415623349499999</v>
+        <v>3.4045260906</v>
       </c>
       <c r="P47">
-        <v>8.3623882005</v>
+        <v>8.335219049400001</v>
       </c>
       <c r="Q47">
-        <v>9.8623882005</v>
+        <v>9.835219049400001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.224442352630001</v>
+        <v>0.2271436937661861</v>
       </c>
       <c r="T47">
-        <v>1.092554390441592</v>
+        <v>1.109075456554801</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.839773838204313</v>
+        <v>7.669343972156394</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1401306946337405</v>
+        <v>0.1399918053209805</v>
       </c>
       <c r="C48">
-        <v>48.32109181069054</v>
+        <v>47.68994351144854</v>
       </c>
       <c r="D48">
-        <v>67.72305181069055</v>
+        <v>67.80716351144855</v>
       </c>
       <c r="E48">
-        <v>32.77596000000001</v>
+        <v>33.49122000000001</v>
       </c>
       <c r="F48">
-        <v>32.90196000000001</v>
+        <v>33.61722000000001</v>
       </c>
       <c r="G48">
         <v>13.5</v>
@@ -5223,45 +5223,45 @@
         <v>13.5</v>
       </c>
       <c r="M48">
-        <v>1.760254860000001</v>
+        <v>1.825415046</v>
       </c>
       <c r="N48">
-        <v>11.73974514</v>
+        <v>11.674584954</v>
       </c>
       <c r="O48">
-        <v>3.4045260906</v>
+        <v>3.38562963666</v>
       </c>
       <c r="P48">
-        <v>8.335219049400001</v>
+        <v>8.288955317340001</v>
       </c>
       <c r="Q48">
-        <v>9.835219049400001</v>
+        <v>9.788955317340001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2271436937661861</v>
+        <v>0.2299469723037367</v>
       </c>
       <c r="T48">
-        <v>1.109075456554801</v>
+        <v>1.126219959125113</v>
       </c>
       <c r="U48">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V48">
         <v>0.29</v>
       </c>
       <c r="W48">
-        <v>0.037985</v>
+        <v>0.038553</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y48">
-        <v>7.669343972156394</v>
+        <v>7.395578353307819</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1399918053209805</v>
+        <v>0.1395916360082204</v>
       </c>
       <c r="C49">
-        <v>47.68994351144854</v>
+        <v>47.21819940523364</v>
       </c>
       <c r="D49">
-        <v>67.80716351144855</v>
+        <v>68.05067940523365</v>
       </c>
       <c r="E49">
-        <v>33.49122000000001</v>
+        <v>34.20648000000001</v>
       </c>
       <c r="F49">
-        <v>33.61722000000001</v>
+        <v>34.33248000000001</v>
       </c>
       <c r="G49">
         <v>13.5</v>
@@ -5305,28 +5305,28 @@
         <v>13.5</v>
       </c>
       <c r="M49">
-        <v>1.825415046</v>
+        <v>1.864253664000001</v>
       </c>
       <c r="N49">
-        <v>11.674584954</v>
+        <v>11.635746336</v>
       </c>
       <c r="O49">
-        <v>3.38562963666</v>
+        <v>3.37436643744</v>
       </c>
       <c r="P49">
-        <v>8.288955317340001</v>
+        <v>8.26137989856</v>
       </c>
       <c r="Q49">
-        <v>9.788955317340001</v>
+        <v>9.76137989856</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2299469723037367</v>
+        <v>0.2328580692465777</v>
       </c>
       <c r="T49">
-        <v>1.126219959125113</v>
+        <v>1.144023865640437</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.395578353307819</v>
+        <v>7.241503804280572</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1395916360082204</v>
+        <v>0.1391914666954604</v>
       </c>
       <c r="C50">
-        <v>47.21819940523365</v>
+        <v>46.74821068057723</v>
       </c>
       <c r="D50">
-        <v>68.05067940523365</v>
+        <v>68.29595068057723</v>
       </c>
       <c r="E50">
-        <v>34.20648000000001</v>
+        <v>34.92174000000001</v>
       </c>
       <c r="F50">
-        <v>34.33248</v>
+        <v>35.04774</v>
       </c>
       <c r="G50">
         <v>13.5</v>
@@ -5387,28 +5387,28 @@
         <v>13.5</v>
       </c>
       <c r="M50">
-        <v>1.864253664</v>
+        <v>1.903092282</v>
       </c>
       <c r="N50">
-        <v>11.635746336</v>
+        <v>11.596907718</v>
       </c>
       <c r="O50">
-        <v>3.37436643744</v>
+        <v>3.36310323822</v>
       </c>
       <c r="P50">
-        <v>8.261379898560001</v>
+        <v>8.233804479780002</v>
       </c>
       <c r="Q50">
-        <v>9.761379898560001</v>
+        <v>9.733804479780002</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2328580692465777</v>
+        <v>0.2358833268538439</v>
       </c>
       <c r="T50">
-        <v>1.144023865640437</v>
+        <v>1.162525964568126</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.241503804280573</v>
+        <v>7.093718012356481</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1391914666954604</v>
+        <v>0.1387912973827003</v>
       </c>
       <c r="C51">
-        <v>46.74821068057723</v>
+        <v>46.27999638660908</v>
       </c>
       <c r="D51">
-        <v>68.29595068057723</v>
+        <v>68.54299638660909</v>
       </c>
       <c r="E51">
-        <v>34.92174000000001</v>
+        <v>35.63700000000001</v>
       </c>
       <c r="F51">
-        <v>35.04774</v>
+        <v>35.76300000000001</v>
       </c>
       <c r="G51">
         <v>13.5</v>
@@ -5469,28 +5469,28 @@
         <v>13.5</v>
       </c>
       <c r="M51">
-        <v>1.903092282</v>
+        <v>1.9419309</v>
       </c>
       <c r="N51">
-        <v>11.596907718</v>
+        <v>11.5580691</v>
       </c>
       <c r="O51">
-        <v>3.36310323822</v>
+        <v>3.351840038999999</v>
       </c>
       <c r="P51">
-        <v>8.233804479780002</v>
+        <v>8.206229061</v>
       </c>
       <c r="Q51">
-        <v>9.733804479780002</v>
+        <v>9.706229061</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2358833268538439</v>
+        <v>0.2390295947654007</v>
       </c>
       <c r="T51">
-        <v>1.162525964568126</v>
+        <v>1.181768147452923</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.093718012356481</v>
+        <v>6.951843652109351</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1387912973827003</v>
+        <v>0.1383911280699403</v>
       </c>
       <c r="C52">
-        <v>46.27999638660908</v>
+        <v>45.81357584908393</v>
       </c>
       <c r="D52">
-        <v>68.54299638660909</v>
+        <v>68.79183584908394</v>
       </c>
       <c r="E52">
-        <v>35.63700000000001</v>
+        <v>36.35226000000001</v>
       </c>
       <c r="F52">
-        <v>35.76300000000001</v>
+        <v>36.47826000000001</v>
       </c>
       <c r="G52">
         <v>13.5</v>
@@ -5551,28 +5551,28 @@
         <v>13.5</v>
       </c>
       <c r="M52">
-        <v>1.9419309</v>
+        <v>1.980769518</v>
       </c>
       <c r="N52">
-        <v>11.5580691</v>
+        <v>11.519230482</v>
       </c>
       <c r="O52">
-        <v>3.351840038999999</v>
+        <v>3.34057683978</v>
       </c>
       <c r="P52">
-        <v>8.206229061</v>
+        <v>8.178653642219999</v>
       </c>
       <c r="Q52">
-        <v>9.706229061</v>
+        <v>9.678653642219999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2390295947654007</v>
+        <v>0.2423042817753884</v>
       </c>
       <c r="T52">
-        <v>1.181768147452923</v>
+        <v>1.201795725557508</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.951843652109351</v>
+        <v>6.815532992264068</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1383911280699403</v>
+        <v>0.1379909587571803</v>
       </c>
       <c r="C53">
-        <v>45.81357584908393</v>
+        <v>45.34896867542105</v>
       </c>
       <c r="D53">
-        <v>68.79183584908394</v>
+        <v>69.04248867542105</v>
       </c>
       <c r="E53">
-        <v>36.35226000000001</v>
+        <v>37.06752000000001</v>
       </c>
       <c r="F53">
-        <v>36.47826000000001</v>
+        <v>37.19352000000001</v>
       </c>
       <c r="G53">
         <v>13.5</v>
@@ -5633,28 +5633,28 @@
         <v>13.5</v>
       </c>
       <c r="M53">
-        <v>1.980769518</v>
+        <v>2.019608136</v>
       </c>
       <c r="N53">
-        <v>11.519230482</v>
+        <v>11.480391864</v>
       </c>
       <c r="O53">
-        <v>3.34057683978</v>
+        <v>3.32931364056</v>
       </c>
       <c r="P53">
-        <v>8.178653642219999</v>
+        <v>8.151078223439999</v>
       </c>
       <c r="Q53">
-        <v>9.678653642219999</v>
+        <v>9.651078223439999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2423042817753884</v>
+        <v>0.2457154140774589</v>
       </c>
       <c r="T53">
-        <v>1.201795725557508</v>
+        <v>1.222657786083117</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.815532992264068</v>
+        <v>6.684465050105144</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1379909587571803</v>
+        <v>0.1375907894444203</v>
       </c>
       <c r="C54">
-        <v>45.34896867542105</v>
+        <v>44.88619475985438</v>
       </c>
       <c r="D54">
-        <v>69.04248867542105</v>
+        <v>69.29497475985438</v>
       </c>
       <c r="E54">
-        <v>37.06752000000001</v>
+        <v>37.78278000000001</v>
       </c>
       <c r="F54">
-        <v>37.19352000000001</v>
+        <v>37.90878000000001</v>
       </c>
       <c r="G54">
         <v>13.5</v>
@@ -5715,28 +5715,28 @@
         <v>13.5</v>
       </c>
       <c r="M54">
-        <v>2.019608136</v>
+        <v>2.058446754</v>
       </c>
       <c r="N54">
-        <v>11.480391864</v>
+        <v>11.441553246</v>
       </c>
       <c r="O54">
-        <v>3.32931364056</v>
+        <v>3.31805044134</v>
       </c>
       <c r="P54">
-        <v>8.151078223439999</v>
+        <v>8.123502804659999</v>
       </c>
       <c r="Q54">
-        <v>9.651078223439999</v>
+        <v>9.623502804659999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2457154140774589</v>
+        <v>0.249271700945575</v>
       </c>
       <c r="T54">
-        <v>1.222657786083117</v>
+        <v>1.244407593865135</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.684465050105144</v>
+        <v>6.558343068027689</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1375907894444203</v>
+        <v>0.1371906201316602</v>
       </c>
       <c r="C55">
-        <v>44.88619475985438</v>
+        <v>44.42527428869627</v>
       </c>
       <c r="D55">
-        <v>69.29497475985438</v>
+        <v>69.54931428869628</v>
       </c>
       <c r="E55">
-        <v>37.78278000000001</v>
+        <v>38.49804000000001</v>
       </c>
       <c r="F55">
-        <v>37.90878000000001</v>
+        <v>38.62404000000001</v>
       </c>
       <c r="G55">
         <v>13.5</v>
@@ -5797,28 +5797,28 @@
         <v>13.5</v>
       </c>
       <c r="M55">
-        <v>2.058446754</v>
+        <v>2.097285372</v>
       </c>
       <c r="N55">
-        <v>11.441553246</v>
+        <v>11.402714628</v>
       </c>
       <c r="O55">
-        <v>3.31805044134</v>
+        <v>3.30678724212</v>
       </c>
       <c r="P55">
-        <v>8.123502804659999</v>
+        <v>8.09592738588</v>
       </c>
       <c r="Q55">
-        <v>9.623502804659999</v>
+        <v>9.59592738588</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.249271700945575</v>
+        <v>0.25298260898187</v>
       </c>
       <c r="T55">
-        <v>1.244407593865135</v>
+        <v>1.267103045463763</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.558343068027689</v>
+        <v>6.43689227047162</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1371906201316602</v>
+        <v>0.1367904508189002</v>
       </c>
       <c r="C56">
-        <v>44.42527428869627</v>
+        <v>43.96622774571728</v>
       </c>
       <c r="D56">
-        <v>69.54931428869628</v>
+        <v>69.80552774571728</v>
       </c>
       <c r="E56">
-        <v>38.49804000000001</v>
+        <v>39.21330000000001</v>
       </c>
       <c r="F56">
-        <v>38.62404000000001</v>
+        <v>39.33930000000001</v>
       </c>
       <c r="G56">
         <v>13.5</v>
@@ -5879,28 +5879,28 @@
         <v>13.5</v>
       </c>
       <c r="M56">
-        <v>2.097285372</v>
+        <v>2.136123990000001</v>
       </c>
       <c r="N56">
-        <v>11.402714628</v>
+        <v>11.36387601</v>
       </c>
       <c r="O56">
-        <v>3.30678724212</v>
+        <v>3.295524042899999</v>
       </c>
       <c r="P56">
-        <v>8.09592738588</v>
+        <v>8.0683519671</v>
       </c>
       <c r="Q56">
-        <v>9.59592738588</v>
+        <v>9.5683519671</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.25298260898187</v>
+        <v>0.2568584462642226</v>
       </c>
       <c r="T56">
-        <v>1.267103045463763</v>
+        <v>1.290807183800107</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.43689227047162</v>
+        <v>6.319857865553954</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1367904508189002</v>
+        <v>0.1363902815061401</v>
       </c>
       <c r="C57">
-        <v>43.96622774571728</v>
+        <v>43.50907591764553</v>
       </c>
       <c r="D57">
-        <v>69.80552774571728</v>
+        <v>70.06363591764554</v>
       </c>
       <c r="E57">
-        <v>39.21330000000001</v>
+        <v>39.92856000000001</v>
       </c>
       <c r="F57">
-        <v>39.33930000000001</v>
+        <v>40.05456000000001</v>
       </c>
       <c r="G57">
         <v>13.5</v>
@@ -5961,28 +5961,28 @@
         <v>13.5</v>
       </c>
       <c r="M57">
-        <v>2.136123990000001</v>
+        <v>2.174962608</v>
       </c>
       <c r="N57">
-        <v>11.36387601</v>
+        <v>11.325037392</v>
       </c>
       <c r="O57">
-        <v>3.295524042899999</v>
+        <v>3.284260843679999</v>
       </c>
       <c r="P57">
-        <v>8.0683519671</v>
+        <v>8.04077654832</v>
       </c>
       <c r="Q57">
-        <v>9.5683519671</v>
+        <v>9.54077654832</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2568584462642226</v>
+        <v>0.2609104579685003</v>
       </c>
       <c r="T57">
-        <v>1.290807183800107</v>
+        <v>1.315588782969921</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.319857865553954</v>
+        <v>6.20700326081192</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1363902815061401</v>
+        <v>0.1363948121933801</v>
       </c>
       <c r="C58">
-        <v>43.50907591764553</v>
+        <v>42.79088295364539</v>
       </c>
       <c r="D58">
-        <v>70.06363591764554</v>
+        <v>70.0607029536454</v>
       </c>
       <c r="E58">
-        <v>39.92856000000001</v>
+        <v>40.64382000000001</v>
       </c>
       <c r="F58">
-        <v>40.05456000000001</v>
+        <v>40.76982000000001</v>
       </c>
       <c r="G58">
         <v>13.5</v>
@@ -6043,45 +6043,45 @@
         <v>13.5</v>
       </c>
       <c r="M58">
-        <v>2.174962608</v>
+        <v>2.254571046000001</v>
       </c>
       <c r="N58">
-        <v>11.325037392</v>
+        <v>11.245428954</v>
       </c>
       <c r="O58">
-        <v>3.284260843679999</v>
+        <v>3.26117439666</v>
       </c>
       <c r="P58">
-        <v>8.04077654832</v>
+        <v>7.98425455734</v>
       </c>
       <c r="Q58">
-        <v>9.54077654832</v>
+        <v>9.48425455734</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2609104579685003</v>
+        <v>0.2651509353334421</v>
       </c>
       <c r="T58">
-        <v>1.315588782969921</v>
+        <v>1.341523014659262</v>
       </c>
       <c r="U58">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V58">
         <v>0.29</v>
       </c>
       <c r="W58">
-        <v>0.038553</v>
+        <v>0.039263</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>6.20700326081192</v>
+        <v>5.987835257598707</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1363948121933801</v>
+        <v>0.13600174288062</v>
       </c>
       <c r="C59">
-        <v>42.79088295364539</v>
+        <v>42.33099522521269</v>
       </c>
       <c r="D59">
-        <v>70.0607029536454</v>
+        <v>70.3160752252127</v>
       </c>
       <c r="E59">
-        <v>40.64382000000001</v>
+        <v>41.35908000000001</v>
       </c>
       <c r="F59">
-        <v>40.76982000000001</v>
+        <v>41.48508000000001</v>
       </c>
       <c r="G59">
         <v>13.5</v>
@@ -6125,28 +6125,28 @@
         <v>13.5</v>
       </c>
       <c r="M59">
-        <v>2.254571046000001</v>
+        <v>2.294124924000001</v>
       </c>
       <c r="N59">
-        <v>11.245428954</v>
+        <v>11.205875076</v>
       </c>
       <c r="O59">
-        <v>3.26117439666</v>
+        <v>3.24970377204</v>
       </c>
       <c r="P59">
-        <v>7.98425455734</v>
+        <v>7.95617130396</v>
       </c>
       <c r="Q59">
-        <v>9.48425455734</v>
+        <v>9.45617130396</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2651509353334421</v>
+        <v>0.2695933401919525</v>
       </c>
       <c r="T59">
-        <v>1.341523014659262</v>
+        <v>1.368692209762381</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.987835257598707</v>
+        <v>5.884596718674592</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1360017428806201</v>
+        <v>0.13560867356786</v>
       </c>
       <c r="C60">
-        <v>42.33099522521268</v>
+        <v>41.87297597864085</v>
       </c>
       <c r="D60">
-        <v>70.31607522521269</v>
+        <v>70.57331597864085</v>
       </c>
       <c r="E60">
-        <v>41.35908000000001</v>
+        <v>42.07434000000001</v>
       </c>
       <c r="F60">
-        <v>41.48508</v>
+        <v>42.20034</v>
       </c>
       <c r="G60">
         <v>13.5</v>
@@ -6207,28 +6207,28 @@
         <v>13.5</v>
       </c>
       <c r="M60">
-        <v>2.294124924</v>
+        <v>2.333678802</v>
       </c>
       <c r="N60">
-        <v>11.205875076</v>
+        <v>11.166321198</v>
       </c>
       <c r="O60">
-        <v>3.24970377204</v>
+        <v>3.23823314742</v>
       </c>
       <c r="P60">
-        <v>7.95617130396</v>
+        <v>7.92808805058</v>
       </c>
       <c r="Q60">
-        <v>9.45617130396</v>
+        <v>9.428088050580001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2695933401919525</v>
+        <v>0.2742524477264878</v>
       </c>
       <c r="T60">
-        <v>1.36869220976238</v>
+        <v>1.397186731455895</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.884596718674593</v>
+        <v>5.78485779123943</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.13560867356786</v>
+        <v>0.1352156042551</v>
       </c>
       <c r="C61">
-        <v>41.87297597864085</v>
+        <v>41.41684579590297</v>
       </c>
       <c r="D61">
-        <v>70.57331597864085</v>
+        <v>70.83244579590297</v>
       </c>
       <c r="E61">
-        <v>42.07434000000001</v>
+        <v>42.78960000000001</v>
       </c>
       <c r="F61">
-        <v>42.20034</v>
+        <v>42.9156</v>
       </c>
       <c r="G61">
         <v>13.5</v>
@@ -6289,28 +6289,28 @@
         <v>13.5</v>
       </c>
       <c r="M61">
-        <v>2.333678802</v>
+        <v>2.373232680000001</v>
       </c>
       <c r="N61">
-        <v>11.166321198</v>
+        <v>11.12676732</v>
       </c>
       <c r="O61">
-        <v>3.23823314742</v>
+        <v>3.2267625228</v>
       </c>
       <c r="P61">
-        <v>7.92808805058</v>
+        <v>7.900004797199999</v>
       </c>
       <c r="Q61">
-        <v>9.428088050580001</v>
+        <v>9.400004797199999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2742524477264878</v>
+        <v>0.2791445106377499</v>
       </c>
       <c r="T61">
-        <v>1.397186731455895</v>
+        <v>1.427105979234086</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.78485779123943</v>
+        <v>5.688443494718772</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1352156042551</v>
+        <v>0.1348225349423399</v>
       </c>
       <c r="C62">
-        <v>41.41684579590297</v>
+        <v>40.96262556237615</v>
       </c>
       <c r="D62">
-        <v>70.83244579590297</v>
+        <v>71.09348556237616</v>
       </c>
       <c r="E62">
-        <v>42.78960000000001</v>
+        <v>43.50486000000001</v>
       </c>
       <c r="F62">
-        <v>42.9156</v>
+        <v>43.63086000000001</v>
       </c>
       <c r="G62">
         <v>13.5</v>
@@ -6371,28 +6371,28 @@
         <v>13.5</v>
       </c>
       <c r="M62">
-        <v>2.373232680000001</v>
+        <v>2.412786558000001</v>
       </c>
       <c r="N62">
-        <v>11.12676732</v>
+        <v>11.087213442</v>
       </c>
       <c r="O62">
-        <v>3.2267625228</v>
+        <v>3.21529189818</v>
       </c>
       <c r="P62">
-        <v>7.900004797199999</v>
+        <v>7.871921543819999</v>
       </c>
       <c r="Q62">
-        <v>9.400004797199999</v>
+        <v>9.371921543819999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2791445106377499</v>
+        <v>0.2842874485701024</v>
       </c>
       <c r="T62">
-        <v>1.427105979234086</v>
+        <v>1.458559547411158</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.688443494718772</v>
+        <v>5.595190322674202</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1348225349423399</v>
+        <v>0.1344294656295799</v>
       </c>
       <c r="C63">
-        <v>40.96262556237615</v>
+        <v>40.5103364724531</v>
       </c>
       <c r="D63">
-        <v>71.09348556237616</v>
+        <v>71.3564564724531</v>
       </c>
       <c r="E63">
-        <v>43.50486000000001</v>
+        <v>44.22012000000001</v>
       </c>
       <c r="F63">
-        <v>43.63086000000001</v>
+        <v>44.34612000000001</v>
       </c>
       <c r="G63">
         <v>13.5</v>
@@ -6453,28 +6453,28 @@
         <v>13.5</v>
       </c>
       <c r="M63">
-        <v>2.412786558000001</v>
+        <v>2.452340436000001</v>
       </c>
       <c r="N63">
-        <v>11.087213442</v>
+        <v>11.047659564</v>
       </c>
       <c r="O63">
-        <v>3.21529189818</v>
+        <v>3.20382127356</v>
       </c>
       <c r="P63">
-        <v>7.871921543819999</v>
+        <v>7.843838290440001</v>
       </c>
       <c r="Q63">
-        <v>9.371921543819999</v>
+        <v>9.343838290440001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2842874485701024</v>
+        <v>0.2897010674462629</v>
       </c>
       <c r="T63">
-        <v>1.458559547411158</v>
+        <v>1.491668566544918</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.595190322674202</v>
+        <v>5.50494531746978</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1344294656295799</v>
+        <v>0.1340363963168199</v>
       </c>
       <c r="C64">
-        <v>40.5103364724531</v>
+        <v>40.06000003527827</v>
       </c>
       <c r="D64">
-        <v>71.3564564724531</v>
+        <v>71.62138003527828</v>
       </c>
       <c r="E64">
-        <v>44.22012000000001</v>
+        <v>44.93538000000001</v>
       </c>
       <c r="F64">
-        <v>44.34612000000001</v>
+        <v>45.06138000000001</v>
       </c>
       <c r="G64">
         <v>13.5</v>
@@ -6535,28 +6535,28 @@
         <v>13.5</v>
       </c>
       <c r="M64">
-        <v>2.452340436000001</v>
+        <v>2.491894314</v>
       </c>
       <c r="N64">
-        <v>11.047659564</v>
+        <v>11.008105686</v>
       </c>
       <c r="O64">
-        <v>3.20382127356</v>
+        <v>3.19235064894</v>
       </c>
       <c r="P64">
-        <v>7.843838290440001</v>
+        <v>7.815755037060001</v>
       </c>
       <c r="Q64">
-        <v>9.343838290440001</v>
+        <v>9.315755037060001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2897010674462629</v>
+        <v>0.2954073143697835</v>
       </c>
       <c r="T64">
-        <v>1.491668566544918</v>
+        <v>1.526567262388611</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.50494531746978</v>
+        <v>5.417565233065497</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1340363963168199</v>
+        <v>0.1336433270040598</v>
       </c>
       <c r="C65">
-        <v>40.06000003527827</v>
+        <v>39.61163808061261</v>
       </c>
       <c r="D65">
-        <v>71.62138003527828</v>
+        <v>71.88827808061262</v>
       </c>
       <c r="E65">
-        <v>44.93538000000001</v>
+        <v>45.65064000000001</v>
       </c>
       <c r="F65">
-        <v>45.06138000000001</v>
+        <v>45.77664000000001</v>
       </c>
       <c r="G65">
         <v>13.5</v>
@@ -6617,28 +6617,28 @@
         <v>13.5</v>
       </c>
       <c r="M65">
-        <v>2.491894314</v>
+        <v>2.531448192</v>
       </c>
       <c r="N65">
-        <v>11.008105686</v>
+        <v>10.968551808</v>
       </c>
       <c r="O65">
-        <v>3.19235064894</v>
+        <v>3.180880024319999</v>
       </c>
       <c r="P65">
-        <v>7.815755037060001</v>
+        <v>7.78767178368</v>
       </c>
       <c r="Q65">
-        <v>9.315755037060001</v>
+        <v>9.28767178368</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2954073143697835</v>
+        <v>0.3014305750112773</v>
       </c>
       <c r="T65">
-        <v>1.526567262388611</v>
+        <v>1.563404774668065</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.417565233065497</v>
+        <v>5.332915776298849</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1336433270040598</v>
+        <v>0.1332502576912998</v>
       </c>
       <c r="C66">
-        <v>39.61163808061261</v>
+        <v>39.1652727648298</v>
       </c>
       <c r="D66">
-        <v>71.88827808061262</v>
+        <v>72.15717276482981</v>
       </c>
       <c r="E66">
-        <v>45.65064000000001</v>
+        <v>46.36590000000001</v>
       </c>
       <c r="F66">
-        <v>45.77664000000001</v>
+        <v>46.49190000000001</v>
       </c>
       <c r="G66">
         <v>13.5</v>
@@ -6699,28 +6699,28 @@
         <v>13.5</v>
       </c>
       <c r="M66">
-        <v>2.531448192</v>
+        <v>2.57100207</v>
       </c>
       <c r="N66">
-        <v>10.968551808</v>
+        <v>10.92899793</v>
       </c>
       <c r="O66">
-        <v>3.180880024319999</v>
+        <v>3.1694093997</v>
       </c>
       <c r="P66">
-        <v>7.78767178368</v>
+        <v>7.7595885303</v>
       </c>
       <c r="Q66">
-        <v>9.28767178368</v>
+        <v>9.2595885303</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3014305750112773</v>
+        <v>0.3077980219751423</v>
       </c>
       <c r="T66">
-        <v>1.563404774668065</v>
+        <v>1.602347287649202</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.332915776298849</v>
+        <v>5.250870918201944</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1332502576912998</v>
+        <v>0.1328571883785398</v>
       </c>
       <c r="C67">
-        <v>39.1652727648298</v>
+        <v>38.72092657704756</v>
       </c>
       <c r="D67">
-        <v>72.15717276482981</v>
+        <v>72.42808657704757</v>
       </c>
       <c r="E67">
-        <v>46.36590000000001</v>
+        <v>47.08116000000001</v>
       </c>
       <c r="F67">
-        <v>46.49190000000001</v>
+        <v>47.20716000000001</v>
       </c>
       <c r="G67">
         <v>13.5</v>
@@ -6781,28 +6781,28 @@
         <v>13.5</v>
       </c>
       <c r="M67">
-        <v>2.57100207</v>
+        <v>2.610555948</v>
       </c>
       <c r="N67">
-        <v>10.92899793</v>
+        <v>10.889444052</v>
       </c>
       <c r="O67">
-        <v>3.1694093997</v>
+        <v>3.15793877508</v>
       </c>
       <c r="P67">
-        <v>7.7595885303</v>
+        <v>7.73150527692</v>
       </c>
       <c r="Q67">
-        <v>9.2595885303</v>
+        <v>9.23150527692</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3077980219751423</v>
+        <v>0.314540024642764</v>
       </c>
       <c r="T67">
-        <v>1.602347287649202</v>
+        <v>1.643580536688053</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.250870918201944</v>
+        <v>5.171312267926157</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1328571883785398</v>
+        <v>0.1324641190657797</v>
       </c>
       <c r="C68">
-        <v>38.72092657704756</v>
+        <v>38.27862234539771</v>
       </c>
       <c r="D68">
-        <v>72.42808657704757</v>
+        <v>72.70104234539772</v>
       </c>
       <c r="E68">
-        <v>47.08116000000001</v>
+        <v>47.79642000000001</v>
       </c>
       <c r="F68">
-        <v>47.20716000000001</v>
+        <v>47.92242000000001</v>
       </c>
       <c r="G68">
         <v>13.5</v>
@@ -6863,28 +6863,28 @@
         <v>13.5</v>
       </c>
       <c r="M68">
-        <v>2.610555948</v>
+        <v>2.650109826</v>
       </c>
       <c r="N68">
-        <v>10.889444052</v>
+        <v>10.849890174</v>
       </c>
       <c r="O68">
-        <v>3.15793877508</v>
+        <v>3.14646815046</v>
       </c>
       <c r="P68">
-        <v>7.73150527692</v>
+        <v>7.703422023539999</v>
       </c>
       <c r="Q68">
-        <v>9.23150527692</v>
+        <v>9.20342202354</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.314540024642764</v>
+        <v>0.3216906335326658</v>
       </c>
       <c r="T68">
-        <v>1.643580536688053</v>
+        <v>1.687312770517137</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.171312267926157</v>
+        <v>5.094128502733229</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1324641190657797</v>
+        <v>0.1320710497530197</v>
       </c>
       <c r="C69">
-        <v>38.27862234539771</v>
+        <v>37.83838324343828</v>
       </c>
       <c r="D69">
-        <v>72.70104234539772</v>
+        <v>72.97606324343829</v>
       </c>
       <c r="E69">
-        <v>47.79642000000001</v>
+        <v>48.51168000000001</v>
       </c>
       <c r="F69">
-        <v>47.92242000000001</v>
+        <v>48.63768000000001</v>
       </c>
       <c r="G69">
         <v>13.5</v>
@@ -6945,28 +6945,28 @@
         <v>13.5</v>
       </c>
       <c r="M69">
-        <v>2.650109826</v>
+        <v>2.689663704000001</v>
       </c>
       <c r="N69">
-        <v>10.849890174</v>
+        <v>10.810336296</v>
       </c>
       <c r="O69">
-        <v>3.14646815046</v>
+        <v>3.134997525839999</v>
       </c>
       <c r="P69">
-        <v>7.703422023539999</v>
+        <v>7.67533877016</v>
       </c>
       <c r="Q69">
-        <v>9.20342202354</v>
+        <v>9.17533877016</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3216906335326658</v>
+        <v>0.3292881554781865</v>
       </c>
       <c r="T69">
-        <v>1.687312770517137</v>
+        <v>1.733778268960539</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.094128502733229</v>
+        <v>5.019214848281269</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1320710497530197</v>
+        <v>0.1316779804402597</v>
       </c>
       <c r="C70">
-        <v>37.83838324343828</v>
+        <v>37.40023279671208</v>
       </c>
       <c r="D70">
-        <v>72.97606324343829</v>
+        <v>73.25317279671209</v>
       </c>
       <c r="E70">
-        <v>48.51168000000001</v>
+        <v>49.22694000000001</v>
       </c>
       <c r="F70">
-        <v>48.63768000000001</v>
+        <v>49.35294000000001</v>
       </c>
       <c r="G70">
         <v>13.5</v>
@@ -7027,28 +7027,28 @@
         <v>13.5</v>
       </c>
       <c r="M70">
-        <v>2.689663704000001</v>
+        <v>2.729217582000001</v>
       </c>
       <c r="N70">
-        <v>10.810336296</v>
+        <v>10.770782418</v>
       </c>
       <c r="O70">
-        <v>3.134997525839999</v>
+        <v>3.12352690122</v>
       </c>
       <c r="P70">
-        <v>7.67533877016</v>
+        <v>7.64725551678</v>
       </c>
       <c r="Q70">
-        <v>9.17533877016</v>
+        <v>9.14725551678</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3292881554781865</v>
+        <v>0.3373758401298699</v>
       </c>
       <c r="T70">
-        <v>1.733778268960539</v>
+        <v>1.783241541497064</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.019214848281269</v>
+        <v>4.946472604103279</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1316779804402597</v>
+        <v>0.1312849111274996</v>
       </c>
       <c r="C71">
-        <v>37.40023279671208</v>
+        <v>36.96419488945497</v>
       </c>
       <c r="D71">
-        <v>73.25317279671209</v>
+        <v>73.53239488945498</v>
       </c>
       <c r="E71">
-        <v>49.22694000000001</v>
+        <v>49.94220000000001</v>
       </c>
       <c r="F71">
-        <v>49.35294000000001</v>
+        <v>50.06820000000001</v>
       </c>
       <c r="G71">
         <v>13.5</v>
@@ -7109,28 +7109,28 @@
         <v>13.5</v>
       </c>
       <c r="M71">
-        <v>2.729217582000001</v>
+        <v>2.768771460000001</v>
       </c>
       <c r="N71">
-        <v>10.770782418</v>
+        <v>10.73122854</v>
       </c>
       <c r="O71">
-        <v>3.12352690122</v>
+        <v>3.1120562766</v>
       </c>
       <c r="P71">
-        <v>7.64725551678</v>
+        <v>7.6191722634</v>
       </c>
       <c r="Q71">
-        <v>9.14725551678</v>
+        <v>9.119172263399999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3373758401298699</v>
+        <v>0.3460027037583321</v>
       </c>
       <c r="T71">
-        <v>1.783241541497064</v>
+        <v>1.836002365536024</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.946472604103279</v>
+        <v>4.875808709758948</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1312849111274996</v>
+        <v>0.1308918418147396</v>
       </c>
       <c r="C72">
-        <v>36.96419488945497</v>
+        <v>36.53029377145823</v>
       </c>
       <c r="D72">
-        <v>73.53239488945498</v>
+        <v>73.81375377145824</v>
       </c>
       <c r="E72">
-        <v>49.94220000000001</v>
+        <v>50.65746000000001</v>
       </c>
       <c r="F72">
-        <v>50.06820000000001</v>
+        <v>50.78346000000001</v>
       </c>
       <c r="G72">
         <v>13.5</v>
@@ -7191,28 +7191,28 @@
         <v>13.5</v>
       </c>
       <c r="M72">
-        <v>2.768771460000001</v>
+        <v>2.808325338000001</v>
       </c>
       <c r="N72">
-        <v>10.73122854</v>
+        <v>10.691674662</v>
       </c>
       <c r="O72">
-        <v>3.1120562766</v>
+        <v>3.100585651979999</v>
       </c>
       <c r="P72">
-        <v>7.6191722634</v>
+        <v>7.591089010019999</v>
       </c>
       <c r="Q72">
-        <v>9.119172263399999</v>
+        <v>9.091089010019999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3460027037583321</v>
+        <v>0.3552245234991021</v>
       </c>
       <c r="T72">
-        <v>1.836002365536024</v>
+        <v>1.892401867094912</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.875808709758948</v>
+        <v>4.807135347649666</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1308918418147396</v>
+        <v>0.1304987725019796</v>
       </c>
       <c r="C73">
-        <v>36.53029377145823</v>
+        <v>36.09855406508916</v>
       </c>
       <c r="D73">
-        <v>73.81375377145824</v>
+        <v>74.09727406508917</v>
       </c>
       <c r="E73">
-        <v>50.65746000000001</v>
+        <v>51.37272000000001</v>
       </c>
       <c r="F73">
-        <v>50.78346000000001</v>
+        <v>51.49872000000001</v>
       </c>
       <c r="G73">
         <v>13.5</v>
@@ -7273,28 +7273,28 @@
         <v>13.5</v>
       </c>
       <c r="M73">
-        <v>2.808325338</v>
+        <v>2.847879216</v>
       </c>
       <c r="N73">
-        <v>10.691674662</v>
+        <v>10.652120784</v>
       </c>
       <c r="O73">
-        <v>3.10058565198</v>
+        <v>3.08911502736</v>
       </c>
       <c r="P73">
-        <v>7.591089010020001</v>
+        <v>7.563005756639999</v>
       </c>
       <c r="Q73">
-        <v>9.091089010020001</v>
+        <v>9.063005756639999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.355224523499102</v>
+        <v>0.3651050446499269</v>
       </c>
       <c r="T73">
-        <v>1.892401867094911</v>
+        <v>1.952829904479434</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.807135347649667</v>
+        <v>4.74036957893231</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1304987725019796</v>
+        <v>0.1301057031892195</v>
       </c>
       <c r="C74">
-        <v>36.09855406508916</v>
+        <v>35.66900077247396</v>
       </c>
       <c r="D74">
-        <v>74.09727406508917</v>
+        <v>74.38298077247397</v>
       </c>
       <c r="E74">
-        <v>51.37272000000001</v>
+        <v>52.08798000000001</v>
       </c>
       <c r="F74">
-        <v>51.49872000000001</v>
+        <v>52.21398000000001</v>
       </c>
       <c r="G74">
         <v>13.5</v>
@@ -7355,28 +7355,28 @@
         <v>13.5</v>
       </c>
       <c r="M74">
-        <v>2.847879216</v>
+        <v>2.887433094</v>
       </c>
       <c r="N74">
-        <v>10.652120784</v>
+        <v>10.612566906</v>
       </c>
       <c r="O74">
-        <v>3.08911502736</v>
+        <v>3.07764440274</v>
       </c>
       <c r="P74">
-        <v>7.563005756639999</v>
+        <v>7.53492250326</v>
       </c>
       <c r="Q74">
-        <v>9.063005756639999</v>
+        <v>9.034922503259999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3651050446499269</v>
+        <v>0.3757174562563685</v>
       </c>
       <c r="T74">
-        <v>1.952829904479434</v>
+        <v>2.017734092781328</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.74036957893231</v>
+        <v>4.675433009357896</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1301057031892195</v>
+        <v>0.1297126338764595</v>
       </c>
       <c r="C75">
-        <v>35.66900077247396</v>
+        <v>35.24165928284755</v>
       </c>
       <c r="D75">
-        <v>74.38298077247397</v>
+        <v>74.67089928284756</v>
       </c>
       <c r="E75">
-        <v>52.08798000000001</v>
+        <v>52.80324000000001</v>
       </c>
       <c r="F75">
-        <v>52.21398000000001</v>
+        <v>52.92924000000001</v>
       </c>
       <c r="G75">
         <v>13.5</v>
@@ -7437,28 +7437,28 @@
         <v>13.5</v>
       </c>
       <c r="M75">
-        <v>2.887433094</v>
+        <v>2.926986972</v>
       </c>
       <c r="N75">
-        <v>10.612566906</v>
+        <v>10.573013028</v>
       </c>
       <c r="O75">
-        <v>3.07764440274</v>
+        <v>3.06617377812</v>
       </c>
       <c r="P75">
-        <v>7.53492250326</v>
+        <v>7.506839249880001</v>
       </c>
       <c r="Q75">
-        <v>9.034922503259999</v>
+        <v>9.006839249880001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3757174562563685</v>
+        <v>0.3871462072171518</v>
       </c>
       <c r="T75">
-        <v>2.017734092781328</v>
+        <v>2.0876309109526</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.675433009357896</v>
+        <v>4.61225148220441</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1297126338764595</v>
+        <v>0.1293195645636994</v>
       </c>
       <c r="C76">
-        <v>35.24165928284755</v>
+        <v>34.81655538007466</v>
       </c>
       <c r="D76">
-        <v>74.67089928284756</v>
+        <v>74.96105538007467</v>
       </c>
       <c r="E76">
-        <v>52.80324000000001</v>
+        <v>53.51850000000001</v>
       </c>
       <c r="F76">
-        <v>52.92924000000001</v>
+        <v>53.64450000000001</v>
       </c>
       <c r="G76">
         <v>13.5</v>
@@ -7519,28 +7519,28 @@
         <v>13.5</v>
       </c>
       <c r="M76">
-        <v>2.926986972</v>
+        <v>2.96654085</v>
       </c>
       <c r="N76">
-        <v>10.573013028</v>
+        <v>10.53345915</v>
       </c>
       <c r="O76">
-        <v>3.06617377812</v>
+        <v>3.054703153499999</v>
       </c>
       <c r="P76">
-        <v>7.506839249880001</v>
+        <v>7.478755996499999</v>
       </c>
       <c r="Q76">
-        <v>9.006839249880001</v>
+        <v>8.978755996499999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3871462072171518</v>
+        <v>0.3994892582547978</v>
       </c>
       <c r="T76">
-        <v>2.0876309109526</v>
+        <v>2.163119474577573</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.61225148220441</v>
+        <v>4.550754795775018</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1293195645636994</v>
+        <v>0.1302754952509394</v>
       </c>
       <c r="C77">
-        <v>34.81655538007466</v>
+        <v>33.3995357041329</v>
       </c>
       <c r="D77">
-        <v>74.96105538007467</v>
+        <v>74.25929570413291</v>
       </c>
       <c r="E77">
-        <v>53.51850000000001</v>
+        <v>54.23376000000001</v>
       </c>
       <c r="F77">
-        <v>53.64450000000001</v>
+        <v>54.35976000000001</v>
       </c>
       <c r="G77">
         <v>13.5</v>
@@ -7601,45 +7601,45 @@
         <v>13.5</v>
       </c>
       <c r="M77">
-        <v>2.96654085</v>
+        <v>3.141994128000001</v>
       </c>
       <c r="N77">
-        <v>10.53345915</v>
+        <v>10.358005872</v>
       </c>
       <c r="O77">
-        <v>3.054703153499999</v>
+        <v>3.00382170288</v>
       </c>
       <c r="P77">
-        <v>7.478755996499999</v>
+        <v>7.35418416912</v>
       </c>
       <c r="Q77">
-        <v>8.978755996499999</v>
+        <v>8.85418416912</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3994892582547978</v>
+        <v>0.4128608968789142</v>
       </c>
       <c r="T77">
-        <v>2.163119474577573</v>
+        <v>2.244898751837961</v>
       </c>
       <c r="U77">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V77">
         <v>0.29</v>
       </c>
       <c r="W77">
-        <v>0.039263</v>
+        <v>0.041038</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y77">
-        <v>4.550754795775018</v>
+        <v>4.296634382507031</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1302754952509394</v>
+        <v>0.1299001759381794</v>
       </c>
       <c r="C78">
-        <v>33.3995357041329</v>
+        <v>32.95822947444813</v>
       </c>
       <c r="D78">
-        <v>74.25929570413291</v>
+        <v>74.53324947444814</v>
       </c>
       <c r="E78">
-        <v>54.23376000000001</v>
+        <v>54.94902000000001</v>
       </c>
       <c r="F78">
-        <v>54.35976000000001</v>
+        <v>55.07502000000001</v>
       </c>
       <c r="G78">
         <v>13.5</v>
@@ -7683,28 +7683,28 @@
         <v>13.5</v>
       </c>
       <c r="M78">
-        <v>3.141994128000001</v>
+        <v>3.183336156000001</v>
       </c>
       <c r="N78">
-        <v>10.358005872</v>
+        <v>10.316663844</v>
       </c>
       <c r="O78">
-        <v>3.00382170288</v>
+        <v>2.99183251476</v>
       </c>
       <c r="P78">
-        <v>7.35418416912</v>
+        <v>7.324831329239999</v>
       </c>
       <c r="Q78">
-        <v>8.85418416912</v>
+        <v>8.824831329239998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4128608968789142</v>
+        <v>0.4273952866877364</v>
       </c>
       <c r="T78">
-        <v>2.244898751837961</v>
+        <v>2.333789270599252</v>
       </c>
       <c r="U78">
         <v>0.0578</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.296634382507031</v>
+        <v>4.240833935980966</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1299001759381794</v>
+        <v>0.1295248566254193</v>
       </c>
       <c r="C79">
-        <v>32.95822947444813</v>
+        <v>32.51895204307145</v>
       </c>
       <c r="D79">
-        <v>74.53324947444814</v>
+        <v>74.80923204307146</v>
       </c>
       <c r="E79">
-        <v>54.94902000000001</v>
+        <v>55.66428000000001</v>
       </c>
       <c r="F79">
-        <v>55.07502000000001</v>
+        <v>55.79028000000001</v>
       </c>
       <c r="G79">
         <v>13.5</v>
@@ -7765,28 +7765,28 @@
         <v>13.5</v>
       </c>
       <c r="M79">
-        <v>3.183336156000001</v>
+        <v>3.224678184000001</v>
       </c>
       <c r="N79">
-        <v>10.316663844</v>
+        <v>10.275321816</v>
       </c>
       <c r="O79">
-        <v>2.99183251476</v>
+        <v>2.979843326639999</v>
       </c>
       <c r="P79">
-        <v>7.324831329239999</v>
+        <v>7.295478489359999</v>
       </c>
       <c r="Q79">
-        <v>8.824831329239998</v>
+        <v>8.795478489359999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4273952866877364</v>
+        <v>0.443250984660997</v>
       </c>
       <c r="T79">
-        <v>2.333789270599252</v>
+        <v>2.430760745611569</v>
       </c>
       <c r="U79">
         <v>0.0578</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.240833935980966</v>
+        <v>4.186464270135055</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1295248566254193</v>
+        <v>0.1291495373126593</v>
       </c>
       <c r="C80">
-        <v>32.51895204307145</v>
+        <v>32.08172603053521</v>
       </c>
       <c r="D80">
-        <v>74.80923204307146</v>
+        <v>75.08726603053522</v>
       </c>
       <c r="E80">
-        <v>55.66428000000001</v>
+        <v>56.37954000000001</v>
       </c>
       <c r="F80">
-        <v>55.79028000000001</v>
+        <v>56.50554000000001</v>
       </c>
       <c r="G80">
         <v>13.5</v>
@@ -7847,28 +7847,28 @@
         <v>13.5</v>
       </c>
       <c r="M80">
-        <v>3.224678184000001</v>
+        <v>3.266020212000001</v>
       </c>
       <c r="N80">
-        <v>10.275321816</v>
+        <v>10.233979788</v>
       </c>
       <c r="O80">
-        <v>2.979843326639999</v>
+        <v>2.967854138519999</v>
       </c>
       <c r="P80">
-        <v>7.295478489359999</v>
+        <v>7.266125649479999</v>
       </c>
       <c r="Q80">
-        <v>8.795478489359999</v>
+        <v>8.766125649479999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.443250984660997</v>
+        <v>0.4606167491079014</v>
       </c>
       <c r="T80">
-        <v>2.430760745611569</v>
+        <v>2.536967599196488</v>
       </c>
       <c r="U80">
         <v>0.0578</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.186464270135055</v>
+        <v>4.133471051525751</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1291495373126593</v>
+        <v>0.1287742179998992</v>
       </c>
       <c r="C81">
-        <v>32.08172603053521</v>
+        <v>31.64657439490961</v>
       </c>
       <c r="D81">
-        <v>75.08726603053522</v>
+        <v>75.36737439490962</v>
       </c>
       <c r="E81">
-        <v>56.37954000000001</v>
+        <v>57.09480000000001</v>
       </c>
       <c r="F81">
-        <v>56.50554000000001</v>
+        <v>57.22080000000001</v>
       </c>
       <c r="G81">
         <v>13.5</v>
@@ -7929,28 +7929,28 @@
         <v>13.5</v>
       </c>
       <c r="M81">
-        <v>3.266020212000001</v>
+        <v>3.307362240000001</v>
       </c>
       <c r="N81">
-        <v>10.233979788</v>
+        <v>10.19263776</v>
       </c>
       <c r="O81">
-        <v>2.967854138519999</v>
+        <v>2.9558649504</v>
       </c>
       <c r="P81">
-        <v>7.266125649479999</v>
+        <v>7.2367728096</v>
       </c>
       <c r="Q81">
-        <v>8.766125649479999</v>
+        <v>8.7367728096</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4606167491079014</v>
+        <v>0.4797190899994963</v>
       </c>
       <c r="T81">
-        <v>2.536967599196488</v>
+        <v>2.653795138139898</v>
       </c>
       <c r="U81">
         <v>0.0578</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.133471051525751</v>
+        <v>4.08180266338168</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1287742179998992</v>
+        <v>0.1283988986871392</v>
       </c>
       <c r="C82">
-        <v>31.64657439490961</v>
+        <v>31.21352043812222</v>
       </c>
       <c r="D82">
-        <v>75.36737439490962</v>
+        <v>75.64958043812223</v>
       </c>
       <c r="E82">
-        <v>57.09480000000001</v>
+        <v>57.81006000000001</v>
       </c>
       <c r="F82">
-        <v>57.22080000000001</v>
+        <v>57.93606000000001</v>
       </c>
       <c r="G82">
         <v>13.5</v>
@@ -8011,28 +8011,28 @@
         <v>13.5</v>
       </c>
       <c r="M82">
-        <v>3.307362240000001</v>
+        <v>3.348704268000001</v>
       </c>
       <c r="N82">
-        <v>10.19263776</v>
+        <v>10.151295732</v>
       </c>
       <c r="O82">
-        <v>2.9558649504</v>
+        <v>2.94387576228</v>
       </c>
       <c r="P82">
-        <v>7.2367728096</v>
+        <v>7.20741996972</v>
       </c>
       <c r="Q82">
-        <v>8.7367728096</v>
+        <v>8.70741996972</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4797190899994963</v>
+        <v>0.5008322036165223</v>
       </c>
       <c r="T82">
-        <v>2.653795138139898</v>
+        <v>2.782920312761563</v>
       </c>
       <c r="U82">
         <v>0.0578</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.08180266338168</v>
+        <v>4.031410037907831</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1283988986871392</v>
+        <v>0.1300612793743792</v>
       </c>
       <c r="C83">
-        <v>31.21352043812222</v>
+        <v>29.26408934194504</v>
       </c>
       <c r="D83">
-        <v>75.64958043812223</v>
+        <v>74.41540934194505</v>
       </c>
       <c r="E83">
-        <v>57.81006000000001</v>
+        <v>58.52532000000001</v>
       </c>
       <c r="F83">
-        <v>57.93606000000001</v>
+        <v>58.65132000000001</v>
       </c>
       <c r="G83">
         <v>13.5</v>
@@ -8093,45 +8093,45 @@
         <v>13.5</v>
       </c>
       <c r="M83">
-        <v>3.348704268000001</v>
+        <v>3.595325916000001</v>
       </c>
       <c r="N83">
-        <v>10.151295732</v>
+        <v>9.904674084</v>
       </c>
       <c r="O83">
-        <v>2.94387576228</v>
+        <v>2.87235548436</v>
       </c>
       <c r="P83">
-        <v>7.20741996972</v>
+        <v>7.03231859964</v>
       </c>
       <c r="Q83">
-        <v>8.70741996972</v>
+        <v>8.53231859964</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5008322036165223</v>
+        <v>0.5242912187465512</v>
       </c>
       <c r="T83">
-        <v>2.782920312761563</v>
+        <v>2.926392729007858</v>
       </c>
       <c r="U83">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V83">
         <v>0.29</v>
       </c>
       <c r="W83">
-        <v>0.041038</v>
+        <v>0.043523</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y83">
-        <v>4.031410037907831</v>
+        <v>3.754875167205842</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1300612793743792</v>
+        <v>0.1297108100616191</v>
       </c>
       <c r="C84">
-        <v>29.26408934194504</v>
+        <v>28.80566040024459</v>
       </c>
       <c r="D84">
-        <v>74.41540934194505</v>
+        <v>74.6722404002446</v>
       </c>
       <c r="E84">
-        <v>58.52532000000001</v>
+        <v>59.24058000000002</v>
       </c>
       <c r="F84">
-        <v>58.65132000000001</v>
+        <v>59.36658000000001</v>
       </c>
       <c r="G84">
         <v>13.5</v>
@@ -8175,28 +8175,28 @@
         <v>13.5</v>
       </c>
       <c r="M84">
-        <v>3.595325916000001</v>
+        <v>3.639171354000001</v>
       </c>
       <c r="N84">
-        <v>9.904674084</v>
+        <v>9.860828645999998</v>
       </c>
       <c r="O84">
-        <v>2.87235548436</v>
+        <v>2.859640307339999</v>
       </c>
       <c r="P84">
-        <v>7.03231859964</v>
+        <v>7.001188338659999</v>
       </c>
       <c r="Q84">
-        <v>8.53231859964</v>
+        <v>8.501188338659999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5242912187465512</v>
+        <v>0.5505101180095244</v>
       </c>
       <c r="T84">
-        <v>2.926392729007858</v>
+        <v>3.086744253047833</v>
       </c>
       <c r="U84">
         <v>0.0613</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.754875167205842</v>
+        <v>3.709635707359988</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1297108100616191</v>
+        <v>0.1293603407488591</v>
       </c>
       <c r="C85">
-        <v>28.80566040024459</v>
+        <v>28.34901040830376</v>
       </c>
       <c r="D85">
-        <v>74.6722404002446</v>
+        <v>74.93085040830377</v>
       </c>
       <c r="E85">
-        <v>59.24058000000002</v>
+        <v>59.95584000000002</v>
       </c>
       <c r="F85">
-        <v>59.36658000000001</v>
+        <v>60.08184000000001</v>
       </c>
       <c r="G85">
         <v>13.5</v>
@@ -8257,28 +8257,28 @@
         <v>13.5</v>
       </c>
       <c r="M85">
-        <v>3.639171354000001</v>
+        <v>3.683016792000001</v>
       </c>
       <c r="N85">
-        <v>9.860828645999998</v>
+        <v>9.816983208</v>
       </c>
       <c r="O85">
-        <v>2.859640307339999</v>
+        <v>2.84692513032</v>
       </c>
       <c r="P85">
-        <v>7.001188338659999</v>
+        <v>6.97005807768</v>
       </c>
       <c r="Q85">
-        <v>8.501188338659999</v>
+        <v>8.470058077680001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5505101180095244</v>
+        <v>0.5800063796803697</v>
       </c>
       <c r="T85">
-        <v>3.086744253047833</v>
+        <v>3.267139717592806</v>
       </c>
       <c r="U85">
         <v>0.0613</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.709635707359988</v>
+        <v>3.665473377510465</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1293603407488591</v>
+        <v>0.1290098714360991</v>
       </c>
       <c r="C86">
-        <v>28.34901040830373</v>
+        <v>27.89415791329775</v>
       </c>
       <c r="D86">
-        <v>74.93085040830374</v>
+        <v>75.19125791329776</v>
       </c>
       <c r="E86">
-        <v>59.95584000000001</v>
+        <v>60.67110000000001</v>
       </c>
       <c r="F86">
-        <v>60.08184000000001</v>
+        <v>60.79710000000001</v>
       </c>
       <c r="G86">
         <v>13.5</v>
@@ -8339,28 +8339,28 @@
         <v>13.5</v>
       </c>
       <c r="M86">
-        <v>3.683016792000001</v>
+        <v>3.72686223</v>
       </c>
       <c r="N86">
-        <v>9.816983208</v>
+        <v>9.77313777</v>
       </c>
       <c r="O86">
-        <v>2.84692513032</v>
+        <v>2.8342099533</v>
       </c>
       <c r="P86">
-        <v>6.97005807768</v>
+        <v>6.9389278167</v>
       </c>
       <c r="Q86">
-        <v>8.470058077680001</v>
+        <v>8.4389278167</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5800063796803694</v>
+        <v>0.6134354762406604</v>
       </c>
       <c r="T86">
-        <v>3.267139717592804</v>
+        <v>3.471587910743773</v>
       </c>
       <c r="U86">
         <v>0.0613</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.665473377510465</v>
+        <v>3.62235016130446</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1290098714360991</v>
+        <v>0.128659402123339</v>
       </c>
       <c r="C87">
-        <v>27.89415791329775</v>
+        <v>27.44112172112911</v>
       </c>
       <c r="D87">
-        <v>75.19125791329776</v>
+        <v>75.45348172112912</v>
       </c>
       <c r="E87">
-        <v>60.67110000000001</v>
+        <v>61.38636000000001</v>
       </c>
       <c r="F87">
-        <v>60.79710000000001</v>
+        <v>61.51236000000001</v>
       </c>
       <c r="G87">
         <v>13.5</v>
@@ -8421,28 +8421,28 @@
         <v>13.5</v>
       </c>
       <c r="M87">
-        <v>3.72686223</v>
+        <v>3.770707668</v>
       </c>
       <c r="N87">
-        <v>9.77313777</v>
+        <v>9.729292332</v>
       </c>
       <c r="O87">
-        <v>2.8342099533</v>
+        <v>2.82149477628</v>
       </c>
       <c r="P87">
-        <v>6.9389278167</v>
+        <v>6.90779755572</v>
       </c>
       <c r="Q87">
-        <v>8.4389278167</v>
+        <v>8.40779755572</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6134354762406604</v>
+        <v>0.6516401580238502</v>
       </c>
       <c r="T87">
-        <v>3.471587910743773</v>
+        <v>3.705242988630594</v>
       </c>
       <c r="U87">
         <v>0.0613</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.62235016130446</v>
+        <v>3.580229810591617</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.128659402123339</v>
+        <v>0.128308932810579</v>
       </c>
       <c r="C88">
-        <v>27.44112172112911</v>
+        <v>26.98992090095522</v>
       </c>
       <c r="D88">
-        <v>75.45348172112912</v>
+        <v>75.71754090095523</v>
       </c>
       <c r="E88">
-        <v>61.38636000000001</v>
+        <v>62.10162000000001</v>
       </c>
       <c r="F88">
-        <v>61.51236000000001</v>
+        <v>62.22762000000001</v>
       </c>
       <c r="G88">
         <v>13.5</v>
@@ -8503,28 +8503,28 @@
         <v>13.5</v>
       </c>
       <c r="M88">
-        <v>3.770707668</v>
+        <v>3.814553106</v>
       </c>
       <c r="N88">
-        <v>9.729292332</v>
+        <v>9.685446894</v>
       </c>
       <c r="O88">
-        <v>2.82149477628</v>
+        <v>2.80877959926</v>
       </c>
       <c r="P88">
-        <v>6.90779755572</v>
+        <v>6.876667294740001</v>
       </c>
       <c r="Q88">
-        <v>8.40779755572</v>
+        <v>8.376667294740001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6516401580238502</v>
+        <v>0.6957224831582999</v>
       </c>
       <c r="T88">
-        <v>3.705242988630594</v>
+        <v>3.974845001576926</v>
       </c>
       <c r="U88">
         <v>0.0613</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.580229810591617</v>
+        <v>3.539077743803208</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.128308932810579</v>
+        <v>0.129707903497819</v>
       </c>
       <c r="C89">
-        <v>26.98992090095522</v>
+        <v>25.23149780190447</v>
       </c>
       <c r="D89">
-        <v>75.71754090095523</v>
+        <v>74.67437780190448</v>
       </c>
       <c r="E89">
-        <v>62.10162000000001</v>
+        <v>62.81688000000001</v>
       </c>
       <c r="F89">
-        <v>62.22762000000001</v>
+        <v>62.94288000000001</v>
       </c>
       <c r="G89">
         <v>13.5</v>
@@ -8585,45 +8585,45 @@
         <v>13.5</v>
       </c>
       <c r="M89">
-        <v>3.814553106</v>
+        <v>4.034638608000001</v>
       </c>
       <c r="N89">
-        <v>9.685446894</v>
+        <v>9.465361391999998</v>
       </c>
       <c r="O89">
-        <v>2.80877959926</v>
+        <v>2.744954803679999</v>
       </c>
       <c r="P89">
-        <v>6.876667294740001</v>
+        <v>6.720406588319999</v>
       </c>
       <c r="Q89">
-        <v>8.376667294740001</v>
+        <v>8.220406588319999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6957224831582999</v>
+        <v>0.7471518624818247</v>
       </c>
       <c r="T89">
-        <v>3.974845001576926</v>
+        <v>4.289380683347648</v>
       </c>
       <c r="U89">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V89">
         <v>0.29</v>
       </c>
       <c r="W89">
-        <v>0.043523</v>
+        <v>0.045511</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y89">
-        <v>3.539077743803208</v>
+        <v>3.34602459145456</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.129707903497819</v>
+        <v>0.1293773141850589</v>
       </c>
       <c r="C90">
-        <v>25.23149780190447</v>
+        <v>24.76014450406743</v>
       </c>
       <c r="D90">
-        <v>74.67437780190448</v>
+        <v>74.91828450406744</v>
       </c>
       <c r="E90">
-        <v>62.81688000000001</v>
+        <v>63.53214000000001</v>
       </c>
       <c r="F90">
-        <v>62.94288000000001</v>
+        <v>63.65814000000001</v>
       </c>
       <c r="G90">
         <v>13.5</v>
@@ -8667,28 +8667,28 @@
         <v>13.5</v>
       </c>
       <c r="M90">
-        <v>4.034638608000001</v>
+        <v>4.080486774000001</v>
       </c>
       <c r="N90">
-        <v>9.465361391999998</v>
+        <v>9.419513225999999</v>
       </c>
       <c r="O90">
-        <v>2.744954803679999</v>
+        <v>2.73165883554</v>
       </c>
       <c r="P90">
-        <v>6.720406588319999</v>
+        <v>6.68785439046</v>
       </c>
       <c r="Q90">
-        <v>8.220406588319999</v>
+        <v>8.18785439046</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7471518624818247</v>
+        <v>0.8079320380459902</v>
       </c>
       <c r="T90">
-        <v>4.289380683347648</v>
+        <v>4.661104670894864</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.34602459145456</v>
+        <v>3.308428809528105</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1293773141850589</v>
+        <v>0.1290467248722989</v>
       </c>
       <c r="C91">
-        <v>24.76014450406743</v>
+        <v>24.29038975796547</v>
       </c>
       <c r="D91">
-        <v>74.91828450406744</v>
+        <v>75.16378975796549</v>
       </c>
       <c r="E91">
-        <v>63.53214000000001</v>
+        <v>64.24740000000001</v>
       </c>
       <c r="F91">
-        <v>63.65814000000001</v>
+        <v>64.37340000000002</v>
       </c>
       <c r="G91">
         <v>13.5</v>
@@ -8749,28 +8749,28 @@
         <v>13.5</v>
       </c>
       <c r="M91">
-        <v>4.080486774000001</v>
+        <v>4.126334940000001</v>
       </c>
       <c r="N91">
-        <v>9.419513225999999</v>
+        <v>9.373665059999999</v>
       </c>
       <c r="O91">
-        <v>2.73165883554</v>
+        <v>2.718362867399999</v>
       </c>
       <c r="P91">
-        <v>6.68785439046</v>
+        <v>6.655302192599999</v>
       </c>
       <c r="Q91">
-        <v>8.18785439046</v>
+        <v>8.155302192599999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8079320380459902</v>
+        <v>0.880868248722989</v>
       </c>
       <c r="T91">
-        <v>4.661104670894864</v>
+        <v>5.107173455951523</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.308428809528105</v>
+        <v>3.271668489422237</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1290467248722989</v>
+        <v>0.1287161355595389</v>
       </c>
       <c r="C92">
-        <v>24.29038975796547</v>
+        <v>23.82224933050267</v>
       </c>
       <c r="D92">
-        <v>75.16378975796549</v>
+        <v>75.41090933050269</v>
       </c>
       <c r="E92">
-        <v>64.24740000000001</v>
+        <v>64.96266000000001</v>
       </c>
       <c r="F92">
-        <v>64.37340000000002</v>
+        <v>65.08866000000002</v>
       </c>
       <c r="G92">
         <v>13.5</v>
@@ -8831,28 +8831,28 @@
         <v>13.5</v>
       </c>
       <c r="M92">
-        <v>4.126334940000001</v>
+        <v>4.172183106000001</v>
       </c>
       <c r="N92">
-        <v>9.373665059999999</v>
+        <v>9.327816893999998</v>
       </c>
       <c r="O92">
-        <v>2.718362867399999</v>
+        <v>2.705066899259999</v>
       </c>
       <c r="P92">
-        <v>6.655302192599999</v>
+        <v>6.622749994739999</v>
       </c>
       <c r="Q92">
-        <v>8.155302192599999</v>
+        <v>8.122749994739998</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.880868248722989</v>
+        <v>0.9700125062170987</v>
       </c>
       <c r="T92">
-        <v>5.107173455951523</v>
+        <v>5.652368637687442</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.271668489422237</v>
+        <v>3.235716088439575</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1287161355595389</v>
+        <v>0.1283855462467788</v>
       </c>
       <c r="C93">
-        <v>23.82224933050267</v>
+        <v>23.35573919661753</v>
       </c>
       <c r="D93">
-        <v>75.41090933050269</v>
+        <v>75.65965919661755</v>
       </c>
       <c r="E93">
-        <v>64.96266000000001</v>
+        <v>65.67792000000001</v>
       </c>
       <c r="F93">
-        <v>65.08866000000002</v>
+        <v>65.80392000000002</v>
       </c>
       <c r="G93">
         <v>13.5</v>
@@ -8913,28 +8913,28 @@
         <v>13.5</v>
       </c>
       <c r="M93">
-        <v>4.172183106000001</v>
+        <v>4.218031272000002</v>
       </c>
       <c r="N93">
-        <v>9.327816893999998</v>
+        <v>9.281968727999999</v>
       </c>
       <c r="O93">
-        <v>2.705066899259999</v>
+        <v>2.691770931119999</v>
       </c>
       <c r="P93">
-        <v>6.622749994739999</v>
+        <v>6.59019779688</v>
       </c>
       <c r="Q93">
-        <v>8.122749994739998</v>
+        <v>8.09019779688</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9700125062170987</v>
+        <v>1.081442828084736</v>
       </c>
       <c r="T93">
-        <v>5.652368637687442</v>
+        <v>6.333862614857338</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.235716088439575</v>
+        <v>3.200545261391318</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1283855462467788</v>
+        <v>0.1280549569340188</v>
       </c>
       <c r="C94">
-        <v>23.35573919661753</v>
+        <v>22.89087554272534</v>
       </c>
       <c r="D94">
-        <v>75.65965919661755</v>
+        <v>75.91005554272536</v>
       </c>
       <c r="E94">
-        <v>65.67792000000001</v>
+        <v>66.39318000000002</v>
       </c>
       <c r="F94">
-        <v>65.80392000000002</v>
+        <v>66.51918000000002</v>
       </c>
       <c r="G94">
         <v>13.5</v>
@@ -8995,28 +8995,28 @@
         <v>13.5</v>
       </c>
       <c r="M94">
-        <v>4.218031272000002</v>
+        <v>4.263879438000002</v>
       </c>
       <c r="N94">
-        <v>9.281968727999999</v>
+        <v>9.236120561999998</v>
       </c>
       <c r="O94">
-        <v>2.691770931119999</v>
+        <v>2.678474962979999</v>
       </c>
       <c r="P94">
-        <v>6.59019779688</v>
+        <v>6.557645599019999</v>
       </c>
       <c r="Q94">
-        <v>8.09019779688</v>
+        <v>8.057645599019999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.081442828084736</v>
+        <v>1.224710384771698</v>
       </c>
       <c r="T94">
-        <v>6.333862614857338</v>
+        <v>7.21006915693292</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.200545261391318</v>
+        <v>3.166130796215068</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1280549569340188</v>
+        <v>0.1277243676212587</v>
       </c>
       <c r="C95">
-        <v>22.89087554272534</v>
+        <v>22.42767477022926</v>
       </c>
       <c r="D95">
-        <v>75.91005554272536</v>
+        <v>76.16211477022928</v>
       </c>
       <c r="E95">
-        <v>66.39318000000002</v>
+        <v>67.10844000000002</v>
       </c>
       <c r="F95">
-        <v>66.51918000000002</v>
+        <v>67.23444000000002</v>
       </c>
       <c r="G95">
         <v>13.5</v>
@@ -9077,28 +9077,28 @@
         <v>13.5</v>
       </c>
       <c r="M95">
-        <v>4.263879438000002</v>
+        <v>4.309727604000002</v>
       </c>
       <c r="N95">
-        <v>9.236120561999998</v>
+        <v>9.190272395999997</v>
       </c>
       <c r="O95">
-        <v>2.678474962979999</v>
+        <v>2.665178994839999</v>
       </c>
       <c r="P95">
-        <v>6.557645599019999</v>
+        <v>6.525093401159999</v>
       </c>
       <c r="Q95">
-        <v>8.057645599019999</v>
+        <v>8.025093401159999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.224710384771698</v>
+        <v>1.415733793687647</v>
       </c>
       <c r="T95">
-        <v>7.21006915693292</v>
+        <v>8.37834454636703</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.166130796215068</v>
+        <v>3.132448553702141</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1277243676212587</v>
+        <v>0.1273937783084987</v>
       </c>
       <c r="C96">
-        <v>22.42767477022926</v>
+        <v>21.96615349910155</v>
       </c>
       <c r="D96">
-        <v>76.16211477022928</v>
+        <v>76.41585349910157</v>
       </c>
       <c r="E96">
-        <v>67.10844000000002</v>
+        <v>67.82370000000002</v>
       </c>
       <c r="F96">
-        <v>67.23444000000002</v>
+        <v>67.94970000000002</v>
       </c>
       <c r="G96">
         <v>13.5</v>
@@ -9159,28 +9159,28 @@
         <v>13.5</v>
       </c>
       <c r="M96">
-        <v>4.309727604000002</v>
+        <v>4.355575770000002</v>
       </c>
       <c r="N96">
-        <v>9.190272395999997</v>
+        <v>9.144424229999998</v>
       </c>
       <c r="O96">
-        <v>2.665178994839999</v>
+        <v>2.651883026699999</v>
       </c>
       <c r="P96">
-        <v>6.525093401159999</v>
+        <v>6.492541203299999</v>
       </c>
       <c r="Q96">
-        <v>8.025093401159999</v>
+        <v>7.992541203299999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.415733793687647</v>
+        <v>1.683166566169976</v>
       </c>
       <c r="T96">
-        <v>8.37834454636703</v>
+        <v>10.01393009157479</v>
       </c>
       <c r="U96">
         <v>0.0641</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.132448553702141</v>
+        <v>3.099475411031593</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1273937783084987</v>
+        <v>0.1270631889957387</v>
       </c>
       <c r="C97">
-        <v>21.96615349910155</v>
+        <v>21.50632857153664</v>
       </c>
       <c r="D97">
-        <v>76.41585349910157</v>
+        <v>76.67128857153666</v>
       </c>
       <c r="E97">
-        <v>67.82370000000002</v>
+        <v>68.53896000000002</v>
       </c>
       <c r="F97">
-        <v>67.94970000000002</v>
+        <v>68.66496000000002</v>
       </c>
       <c r="G97">
         <v>13.5</v>
@@ -9241,28 +9241,28 @@
         <v>13.5</v>
       </c>
       <c r="M97">
-        <v>4.355575770000002</v>
+        <v>4.401423936000001</v>
       </c>
       <c r="N97">
-        <v>9.144424229999998</v>
+        <v>9.098576064</v>
       </c>
       <c r="O97">
-        <v>2.651883026699999</v>
+        <v>2.63858705856</v>
       </c>
       <c r="P97">
-        <v>6.492541203299999</v>
+        <v>6.45998900544</v>
       </c>
       <c r="Q97">
-        <v>7.992541203299999</v>
+        <v>7.95998900544</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.683166566169976</v>
+        <v>2.08431572489347</v>
       </c>
       <c r="T97">
-        <v>10.01393009157479</v>
+        <v>12.46730840938642</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.099475411031593</v>
+        <v>3.067189208833347</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1270631889957387</v>
+        <v>0.1267325996829786</v>
       </c>
       <c r="C98">
-        <v>21.50632857153666</v>
+        <v>21.04821705567763</v>
       </c>
       <c r="D98">
-        <v>76.67128857153666</v>
+        <v>76.92843705567763</v>
       </c>
       <c r="E98">
-        <v>68.53896</v>
+        <v>69.25422</v>
       </c>
       <c r="F98">
-        <v>68.66496000000001</v>
+        <v>69.38022000000001</v>
       </c>
       <c r="G98">
         <v>13.5</v>
@@ -9323,28 +9323,28 @@
         <v>13.5</v>
       </c>
       <c r="M98">
-        <v>4.401423936</v>
+        <v>4.447272102000001</v>
       </c>
       <c r="N98">
-        <v>9.098576064</v>
+        <v>9.052727897999999</v>
       </c>
       <c r="O98">
-        <v>2.63858705856</v>
+        <v>2.625291090419999</v>
       </c>
       <c r="P98">
-        <v>6.45998900544</v>
+        <v>6.427436807579999</v>
       </c>
       <c r="Q98">
-        <v>7.95998900544</v>
+        <v>7.927436807579999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.084315724893465</v>
+        <v>2.752897656099285</v>
       </c>
       <c r="T98">
-        <v>12.46730840938639</v>
+        <v>16.55627227240576</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.067189208833347</v>
+        <v>3.035568701525787</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1267325996829786</v>
+        <v>0.1264020103702186</v>
       </c>
       <c r="C99">
-        <v>21.04821705567763</v>
+        <v>20.59183624941819</v>
       </c>
       <c r="D99">
-        <v>76.92843705567763</v>
+        <v>77.1873162494182</v>
       </c>
       <c r="E99">
-        <v>69.25422</v>
+        <v>69.96948</v>
       </c>
       <c r="F99">
-        <v>69.38022000000001</v>
+        <v>70.09548000000001</v>
       </c>
       <c r="G99">
         <v>13.5</v>
@@ -9405,28 +9405,28 @@
         <v>13.5</v>
       </c>
       <c r="M99">
-        <v>4.447272102000001</v>
+        <v>4.493120268000001</v>
       </c>
       <c r="N99">
-        <v>9.052727897999999</v>
+        <v>9.006879731999998</v>
       </c>
       <c r="O99">
-        <v>2.625291090419999</v>
+        <v>2.611995122279999</v>
       </c>
       <c r="P99">
-        <v>6.427436807579999</v>
+        <v>6.394884609719998</v>
       </c>
       <c r="Q99">
-        <v>7.927436807579999</v>
+        <v>7.894884609719998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.752897656099285</v>
+        <v>4.090061518510927</v>
       </c>
       <c r="T99">
-        <v>16.55627227240576</v>
+        <v>24.7341999984445</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.035568701525787</v>
+        <v>3.004593510693891</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1264020103702186</v>
+        <v>0.1315540410574586</v>
       </c>
       <c r="C100">
-        <v>20.59183624941819</v>
+        <v>16.0302456317923</v>
       </c>
       <c r="D100">
-        <v>77.1873162494182</v>
+        <v>73.34098563179231</v>
       </c>
       <c r="E100">
-        <v>69.96948</v>
+        <v>70.68474000000001</v>
       </c>
       <c r="F100">
-        <v>70.09548000000001</v>
+        <v>70.81074000000001</v>
       </c>
       <c r="G100">
         <v>13.5</v>
@@ -9487,129 +9487,47 @@
         <v>13.5</v>
       </c>
       <c r="M100">
-        <v>4.493120268000001</v>
+        <v>5.091292206000001</v>
       </c>
       <c r="N100">
-        <v>9.006879731999998</v>
+        <v>8.408707793999998</v>
       </c>
       <c r="O100">
-        <v>2.611995122279999</v>
+        <v>2.438525260259999</v>
       </c>
       <c r="P100">
-        <v>6.394884609719998</v>
+        <v>5.970182533739999</v>
       </c>
       <c r="Q100">
-        <v>7.894884609719998</v>
+        <v>7.470182533739999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.090061518510927</v>
+        <v>8.10155310574585</v>
       </c>
       <c r="T100">
-        <v>24.7341999984445</v>
+        <v>49.26798317656073</v>
       </c>
       <c r="U100">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V100">
         <v>0.29</v>
       </c>
       <c r="W100">
-        <v>0.045511</v>
+        <v>0.051049</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y100">
-        <v>3.004593510693891</v>
+        <v>2.6515861698314</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1315540410574586</v>
-      </c>
-      <c r="C101">
-        <v>16.0302456317923</v>
-      </c>
-      <c r="D101">
-        <v>73.34098563179231</v>
-      </c>
-      <c r="E101">
-        <v>70.68474000000001</v>
-      </c>
-      <c r="F101">
-        <v>70.81074000000001</v>
-      </c>
-      <c r="G101">
-        <v>13.5</v>
-      </c>
-      <c r="H101">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>15</v>
-      </c>
-      <c r="K101">
-        <v>1.5</v>
-      </c>
-      <c r="L101">
-        <v>13.5</v>
-      </c>
-      <c r="M101">
-        <v>5.091292206000001</v>
-      </c>
-      <c r="N101">
-        <v>8.408707793999998</v>
-      </c>
-      <c r="O101">
-        <v>2.438525260259999</v>
-      </c>
-      <c r="P101">
-        <v>5.970182533739999</v>
-      </c>
-      <c r="Q101">
-        <v>7.470182533739999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.10155310574585</v>
-      </c>
-      <c r="T101">
-        <v>49.26798317656073</v>
-      </c>
-      <c r="U101">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.29</v>
-      </c>
-      <c r="W101">
-        <v>0.051049</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B1/B+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.6515861698314</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
